--- a/research/traditional_assets/database/data/hungary/hungary_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_drugs_pharmaceutical.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1065594692142295</v>
+        <v>0.1065045156919367</v>
       </c>
       <c r="C2">
-        <v>5052.984357411383</v>
+        <v>5007.331521168112</v>
       </c>
       <c r="D2">
-        <v>4845.184357411383</v>
+        <v>4849.570521168112</v>
       </c>
       <c r="E2">
-        <v>-238.8</v>
+        <v>-188.761</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>50.03900000000001</v>
       </c>
       <c r="G2">
         <v>207.8</v>
@@ -1579,28 +1579,28 @@
         <v>737.8</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.5169617</v>
       </c>
       <c r="N2">
-        <v>737.8</v>
+        <v>735.2830382999999</v>
       </c>
       <c r="O2">
-        <v>66.40199999999999</v>
+        <v>66.17547344699999</v>
       </c>
       <c r="P2">
-        <v>671.3979999999999</v>
+        <v>669.107564853</v>
       </c>
       <c r="Q2">
-        <v>798.198</v>
+        <v>795.9075648530001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1065594692142295</v>
+        <v>0.1071179653453906</v>
       </c>
       <c r="T2">
-        <v>0.8841243102286289</v>
+        <v>0.8922511094438618</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>293.1311986193512</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1065045156919367</v>
+        <v>0.1064495621696439</v>
       </c>
       <c r="C3">
-        <v>5007.331521168112</v>
+        <v>4961.686633379509</v>
       </c>
       <c r="D3">
-        <v>4849.570521168112</v>
+        <v>4853.964633379509</v>
       </c>
       <c r="E3">
-        <v>-188.761</v>
+        <v>-138.722</v>
       </c>
       <c r="F3">
-        <v>50.03900000000001</v>
+        <v>100.078</v>
       </c>
       <c r="G3">
         <v>207.8</v>
@@ -1661,28 +1661,28 @@
         <v>737.8</v>
       </c>
       <c r="M3">
-        <v>2.5169617</v>
+        <v>5.033923400000001</v>
       </c>
       <c r="N3">
-        <v>735.2830382999999</v>
+        <v>732.7660765999999</v>
       </c>
       <c r="O3">
-        <v>66.17547344699999</v>
+        <v>65.94894689399999</v>
       </c>
       <c r="P3">
-        <v>669.107564853</v>
+        <v>666.8171297059999</v>
       </c>
       <c r="Q3">
-        <v>795.9075648530001</v>
+        <v>793.617129706</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1071179653453906</v>
+        <v>0.1076878593567795</v>
       </c>
       <c r="T3">
-        <v>0.8922511094438618</v>
+        <v>0.9005437617043035</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>293.1311986193512</v>
+        <v>146.5655993096756</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1064495621696439</v>
+        <v>0.106394608647351</v>
       </c>
       <c r="C4">
-        <v>4961.686633379509</v>
+        <v>4916.049715671043</v>
       </c>
       <c r="D4">
-        <v>4853.964633379509</v>
+        <v>4858.366715671043</v>
       </c>
       <c r="E4">
-        <v>-138.722</v>
+        <v>-88.68299999999999</v>
       </c>
       <c r="F4">
-        <v>100.078</v>
+        <v>150.117</v>
       </c>
       <c r="G4">
         <v>207.8</v>
@@ -1743,28 +1743,28 @@
         <v>737.8</v>
       </c>
       <c r="M4">
-        <v>5.033923400000001</v>
+        <v>7.5508851</v>
       </c>
       <c r="N4">
-        <v>732.7660765999999</v>
+        <v>730.2491149</v>
       </c>
       <c r="O4">
-        <v>65.94894689399999</v>
+        <v>65.722420341</v>
       </c>
       <c r="P4">
-        <v>666.8171297059999</v>
+        <v>664.526694559</v>
       </c>
       <c r="Q4">
-        <v>793.617129706</v>
+        <v>791.3266945590001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1076878593567795</v>
+        <v>0.1082695037601557</v>
       </c>
       <c r="T4">
-        <v>0.9005437617043035</v>
+        <v>0.909007396485579</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>146.5655993096756</v>
+        <v>97.71039953978375</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.106394608647351</v>
+        <v>0.1063396551250582</v>
       </c>
       <c r="C5">
-        <v>4916.049715671043</v>
+        <v>4870.420789746702</v>
       </c>
       <c r="D5">
-        <v>4858.366715671043</v>
+        <v>4862.776789746702</v>
       </c>
       <c r="E5">
-        <v>-88.68299999999999</v>
+        <v>-38.64399999999998</v>
       </c>
       <c r="F5">
-        <v>150.117</v>
+        <v>200.156</v>
       </c>
       <c r="G5">
         <v>207.8</v>
@@ -1825,28 +1825,28 @@
         <v>737.8</v>
       </c>
       <c r="M5">
-        <v>7.5508851</v>
+        <v>10.0678468</v>
       </c>
       <c r="N5">
-        <v>730.2491149</v>
+        <v>727.7321532</v>
       </c>
       <c r="O5">
-        <v>65.722420341</v>
+        <v>65.49589378799999</v>
       </c>
       <c r="P5">
-        <v>664.526694559</v>
+        <v>662.236259412</v>
       </c>
       <c r="Q5">
-        <v>791.3266945590001</v>
+        <v>789.036259412</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1082695037601557</v>
+        <v>0.108863265755269</v>
       </c>
       <c r="T5">
-        <v>0.909007396485579</v>
+        <v>0.9176473569914644</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>97.71039953978375</v>
+        <v>73.2827996548378</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1063396551250582</v>
+        <v>0.1062847016027654</v>
       </c>
       <c r="C6">
-        <v>4870.420789746702</v>
+        <v>4824.799877389348</v>
       </c>
       <c r="D6">
-        <v>4862.776789746702</v>
+        <v>4867.194877389347</v>
       </c>
       <c r="E6">
-        <v>-38.64399999999998</v>
+        <v>11.39500000000004</v>
       </c>
       <c r="F6">
-        <v>200.156</v>
+        <v>250.1950000000001</v>
       </c>
       <c r="G6">
         <v>207.8</v>
@@ -1907,28 +1907,28 @@
         <v>737.8</v>
       </c>
       <c r="M6">
-        <v>10.0678468</v>
+        <v>12.5848085</v>
       </c>
       <c r="N6">
-        <v>727.7321532</v>
+        <v>725.2151914999999</v>
       </c>
       <c r="O6">
-        <v>65.49589378799999</v>
+        <v>65.26936723499999</v>
       </c>
       <c r="P6">
-        <v>662.236259412</v>
+        <v>659.9458242649999</v>
       </c>
       <c r="Q6">
-        <v>789.036259412</v>
+        <v>786.745824265</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.108863265755269</v>
+        <v>0.109469528002911</v>
       </c>
       <c r="T6">
-        <v>0.9176473569914644</v>
+        <v>0.9264692114027369</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>73.2827996548378</v>
+        <v>58.62623972387024</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1062847016027654</v>
+        <v>0.1062297480804726</v>
       </c>
       <c r="C7">
-        <v>4824.799877389348</v>
+        <v>4779.18700046108</v>
       </c>
       <c r="D7">
-        <v>4867.194877389347</v>
+        <v>4871.62100046108</v>
       </c>
       <c r="E7">
-        <v>11.39500000000004</v>
+        <v>61.43400000000003</v>
       </c>
       <c r="F7">
-        <v>250.1950000000001</v>
+        <v>300.234</v>
       </c>
       <c r="G7">
         <v>207.8</v>
@@ -1989,28 +1989,28 @@
         <v>737.8</v>
       </c>
       <c r="M7">
-        <v>12.5848085</v>
+        <v>15.1017702</v>
       </c>
       <c r="N7">
-        <v>725.2151914999999</v>
+        <v>722.6982297999999</v>
       </c>
       <c r="O7">
-        <v>65.26936723499999</v>
+        <v>65.04284068199999</v>
       </c>
       <c r="P7">
-        <v>659.9458242649999</v>
+        <v>657.6553891179999</v>
       </c>
       <c r="Q7">
-        <v>786.745824265</v>
+        <v>784.455389118</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.109469528002911</v>
+        <v>0.1100886894473113</v>
       </c>
       <c r="T7">
-        <v>0.9264692114027369</v>
+        <v>0.9354787648440366</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>58.62623972387024</v>
+        <v>48.85519976989187</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1062297480804726</v>
+        <v>0.1061747945581798</v>
       </c>
       <c r="C8">
-        <v>4779.18700046108</v>
+        <v>4733.5821809036</v>
       </c>
       <c r="D8">
-        <v>4871.62100046108</v>
+        <v>4876.0551809036</v>
       </c>
       <c r="E8">
-        <v>61.43400000000003</v>
+        <v>111.473</v>
       </c>
       <c r="F8">
-        <v>300.234</v>
+        <v>350.273</v>
       </c>
       <c r="G8">
         <v>207.8</v>
@@ -2071,28 +2071,28 @@
         <v>737.8</v>
       </c>
       <c r="M8">
-        <v>15.1017702</v>
+        <v>17.6187319</v>
       </c>
       <c r="N8">
-        <v>722.6982297999999</v>
+        <v>720.1812680999999</v>
       </c>
       <c r="O8">
-        <v>65.04284068199999</v>
+        <v>64.81631412899999</v>
       </c>
       <c r="P8">
-        <v>657.6553891179999</v>
+        <v>655.3649539709999</v>
       </c>
       <c r="Q8">
-        <v>784.455389118</v>
+        <v>782.1649539709999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1100886894473113</v>
+        <v>0.1107211661915912</v>
       </c>
       <c r="T8">
-        <v>0.9354787648440366</v>
+        <v>0.9446820721227833</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>48.85519976989187</v>
+        <v>41.87588551705017</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1061747945581798</v>
+        <v>0.106119841035887</v>
       </c>
       <c r="C9">
-        <v>4733.582180903599</v>
+        <v>4687.985440738556</v>
       </c>
       <c r="D9">
-        <v>4876.055180903599</v>
+        <v>4880.497440738555</v>
       </c>
       <c r="E9">
-        <v>111.4730000000001</v>
+        <v>161.5120000000001</v>
       </c>
       <c r="F9">
-        <v>350.2730000000001</v>
+        <v>400.3120000000001</v>
       </c>
       <c r="G9">
         <v>207.8</v>
@@ -2153,28 +2153,28 @@
         <v>737.8</v>
       </c>
       <c r="M9">
-        <v>17.6187319</v>
+        <v>20.1356936</v>
       </c>
       <c r="N9">
-        <v>720.1812680999999</v>
+        <v>717.6643064</v>
       </c>
       <c r="O9">
-        <v>64.81631412899999</v>
+        <v>64.58978757599999</v>
       </c>
       <c r="P9">
-        <v>655.3649539709999</v>
+        <v>653.0745188240001</v>
       </c>
       <c r="Q9">
-        <v>782.1649539709999</v>
+        <v>779.8745188240001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1107211661915912</v>
+        <v>0.111367392430312</v>
       </c>
       <c r="T9">
-        <v>0.9446820721227834</v>
+        <v>0.9540854512988943</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>41.87588551705016</v>
+        <v>36.6413998274189</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.106119841035887</v>
+        <v>0.1060648875135942</v>
       </c>
       <c r="C10">
-        <v>4687.985440738556</v>
+        <v>4642.396802067929</v>
       </c>
       <c r="D10">
-        <v>4880.497440738555</v>
+        <v>4884.947802067929</v>
       </c>
       <c r="E10">
-        <v>161.5120000000001</v>
+        <v>211.551</v>
       </c>
       <c r="F10">
-        <v>400.3120000000001</v>
+        <v>450.3510000000001</v>
       </c>
       <c r="G10">
         <v>207.8</v>
@@ -2235,28 +2235,28 @@
         <v>737.8</v>
       </c>
       <c r="M10">
-        <v>20.1356936</v>
+        <v>22.6526553</v>
       </c>
       <c r="N10">
-        <v>717.6643064</v>
+        <v>715.1473447</v>
       </c>
       <c r="O10">
-        <v>64.58978757599999</v>
+        <v>64.36326102299999</v>
       </c>
       <c r="P10">
-        <v>653.0745188240001</v>
+        <v>650.784083677</v>
       </c>
       <c r="Q10">
-        <v>779.8745188240001</v>
+        <v>777.5840836770001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.111367392430312</v>
+        <v>0.1120278214435101</v>
       </c>
       <c r="T10">
-        <v>0.9540854512988943</v>
+        <v>0.9636954981492056</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.6413998274189</v>
+        <v>32.57013317992791</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1060648875135942</v>
+        <v>0.1060099339913014</v>
       </c>
       <c r="C11">
-        <v>4642.396802067929</v>
+        <v>4596.816287074388</v>
       </c>
       <c r="D11">
-        <v>4884.947802067929</v>
+        <v>4889.406287074388</v>
       </c>
       <c r="E11">
-        <v>211.551</v>
+        <v>261.59</v>
       </c>
       <c r="F11">
-        <v>450.3510000000001</v>
+        <v>500.39</v>
       </c>
       <c r="G11">
         <v>207.8</v>
@@ -2317,28 +2317,28 @@
         <v>737.8</v>
       </c>
       <c r="M11">
-        <v>22.6526553</v>
+        <v>25.169617</v>
       </c>
       <c r="N11">
-        <v>715.1473447</v>
+        <v>712.6303829999999</v>
       </c>
       <c r="O11">
-        <v>64.36326102299999</v>
+        <v>64.13673446999999</v>
       </c>
       <c r="P11">
-        <v>650.784083677</v>
+        <v>648.49364853</v>
       </c>
       <c r="Q11">
-        <v>777.5840836770001</v>
+        <v>775.29364853</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1120278214435101</v>
+        <v>0.1127029266570016</v>
       </c>
       <c r="T11">
-        <v>0.9636954981492056</v>
+        <v>0.9735191015961904</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.57013317992791</v>
+        <v>29.31311986193512</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1060099339913014</v>
+        <v>0.1059549804690086</v>
       </c>
       <c r="C12">
-        <v>4596.816287074388</v>
+        <v>4551.243918021662</v>
       </c>
       <c r="D12">
-        <v>4889.406287074388</v>
+        <v>4893.872918021661</v>
       </c>
       <c r="E12">
-        <v>261.5900000000001</v>
+        <v>311.6290000000001</v>
       </c>
       <c r="F12">
-        <v>500.3900000000001</v>
+        <v>550.4290000000001</v>
       </c>
       <c r="G12">
         <v>207.8</v>
@@ -2399,28 +2399,28 @@
         <v>737.8</v>
       </c>
       <c r="M12">
-        <v>25.169617</v>
+        <v>27.6865787</v>
       </c>
       <c r="N12">
-        <v>712.6303829999999</v>
+        <v>710.1134212999999</v>
       </c>
       <c r="O12">
-        <v>64.13673446999999</v>
+        <v>63.91020791699999</v>
       </c>
       <c r="P12">
-        <v>648.49364853</v>
+        <v>646.2032133829999</v>
       </c>
       <c r="Q12">
-        <v>775.29364853</v>
+        <v>773.003213383</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1127029266570016</v>
+        <v>0.113393202774167</v>
       </c>
       <c r="T12">
-        <v>0.9735191015961904</v>
+        <v>0.9835634601768151</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>29.31311986193512</v>
+        <v>26.64829078357738</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1059549804690086</v>
+        <v>0.1059000269467158</v>
       </c>
       <c r="C13">
-        <v>4551.243918021662</v>
+        <v>4505.679717254899</v>
       </c>
       <c r="D13">
-        <v>4893.872918021661</v>
+        <v>4898.347717254898</v>
       </c>
       <c r="E13">
-        <v>311.6290000000001</v>
+        <v>361.6680000000001</v>
       </c>
       <c r="F13">
-        <v>550.4290000000001</v>
+        <v>600.4680000000001</v>
       </c>
       <c r="G13">
         <v>207.8</v>
@@ -2481,28 +2481,28 @@
         <v>737.8</v>
       </c>
       <c r="M13">
-        <v>27.6865787</v>
+        <v>30.2035404</v>
       </c>
       <c r="N13">
-        <v>710.1134212999999</v>
+        <v>707.5964596</v>
       </c>
       <c r="O13">
-        <v>63.91020791699999</v>
+        <v>63.68368136399999</v>
       </c>
       <c r="P13">
-        <v>646.2032133829999</v>
+        <v>643.912778236</v>
       </c>
       <c r="Q13">
-        <v>773.003213383</v>
+        <v>770.7127782360001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.113393202774167</v>
+        <v>0.1140991669849043</v>
       </c>
       <c r="T13">
-        <v>0.9835634601768151</v>
+        <v>0.9938360996342723</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.64829078357738</v>
+        <v>24.42759988494594</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1059000269467158</v>
+        <v>0.105845073424423</v>
       </c>
       <c r="C14">
-        <v>4505.679717254899</v>
+        <v>4460.123707201057</v>
       </c>
       <c r="D14">
-        <v>4898.347717254898</v>
+        <v>4902.830707201058</v>
       </c>
       <c r="E14">
-        <v>361.6680000000001</v>
+        <v>411.7070000000001</v>
       </c>
       <c r="F14">
-        <v>600.4680000000001</v>
+        <v>650.5070000000001</v>
       </c>
       <c r="G14">
         <v>207.8</v>
@@ -2563,28 +2563,28 @@
         <v>737.8</v>
       </c>
       <c r="M14">
-        <v>30.2035404</v>
+        <v>32.7205021</v>
       </c>
       <c r="N14">
-        <v>707.5964596</v>
+        <v>705.0794979</v>
       </c>
       <c r="O14">
-        <v>63.68368136399999</v>
+        <v>63.457154811</v>
       </c>
       <c r="P14">
-        <v>643.912778236</v>
+        <v>641.622343089</v>
       </c>
       <c r="Q14">
-        <v>770.7127782360001</v>
+        <v>768.422343089</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1140991669849043</v>
+        <v>0.1148213602579574</v>
       </c>
       <c r="T14">
-        <v>0.9938360996342723</v>
+        <v>1.004344891722936</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.42759988494594</v>
+        <v>22.54855373995009</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.105845073424423</v>
+        <v>0.1057901199021302</v>
       </c>
       <c r="C15">
-        <v>4460.123707201057</v>
+        <v>4414.575910369271</v>
       </c>
       <c r="D15">
-        <v>4902.830707201058</v>
+        <v>4907.321910369271</v>
       </c>
       <c r="E15">
-        <v>411.7070000000001</v>
+        <v>461.7460000000002</v>
       </c>
       <c r="F15">
-        <v>650.5070000000001</v>
+        <v>700.5460000000002</v>
       </c>
       <c r="G15">
         <v>207.8</v>
@@ -2645,28 +2645,28 @@
         <v>737.8</v>
       </c>
       <c r="M15">
-        <v>32.7205021</v>
+        <v>35.23746380000001</v>
       </c>
       <c r="N15">
-        <v>705.0794979</v>
+        <v>702.5625362</v>
       </c>
       <c r="O15">
-        <v>63.457154811</v>
+        <v>63.230628258</v>
       </c>
       <c r="P15">
-        <v>641.622343089</v>
+        <v>639.3319079419999</v>
       </c>
       <c r="Q15">
-        <v>768.422343089</v>
+        <v>766.131907942</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1148213602579574</v>
+        <v>0.1155603487234072</v>
       </c>
       <c r="T15">
-        <v>1.004344891722936</v>
+        <v>1.015098074325289</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.54855373995009</v>
+        <v>20.93794275852509</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1057901199021302</v>
+        <v>0.1057351663798374</v>
       </c>
       <c r="C16">
-        <v>4414.575910369271</v>
+        <v>4369.036349351229</v>
       </c>
       <c r="D16">
-        <v>4907.321910369271</v>
+        <v>4911.821349351228</v>
       </c>
       <c r="E16">
-        <v>461.7460000000002</v>
+        <v>511.7850000000001</v>
       </c>
       <c r="F16">
-        <v>700.5460000000002</v>
+        <v>750.5850000000002</v>
       </c>
       <c r="G16">
         <v>207.8</v>
@@ -2727,28 +2727,28 @@
         <v>737.8</v>
       </c>
       <c r="M16">
-        <v>35.23746380000001</v>
+        <v>37.7544255</v>
       </c>
       <c r="N16">
-        <v>702.5625362</v>
+        <v>700.0455744999999</v>
       </c>
       <c r="O16">
-        <v>63.230628258</v>
+        <v>63.00410170499999</v>
       </c>
       <c r="P16">
-        <v>639.3319079419999</v>
+        <v>637.0414727949999</v>
       </c>
       <c r="Q16">
-        <v>766.131907942</v>
+        <v>763.841472795</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1155603487234072</v>
+        <v>0.1163167251527499</v>
       </c>
       <c r="T16">
-        <v>1.015098074325289</v>
+        <v>1.026104272988873</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.93794275852509</v>
+        <v>19.54207990795675</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1057351663798374</v>
+        <v>0.1056802128575445</v>
       </c>
       <c r="C17">
-        <v>4369.036349351229</v>
+        <v>4323.505046821544</v>
       </c>
       <c r="D17">
-        <v>4911.821349351228</v>
+        <v>4916.329046821544</v>
       </c>
       <c r="E17">
-        <v>511.785</v>
+        <v>561.8240000000001</v>
       </c>
       <c r="F17">
-        <v>750.585</v>
+        <v>800.6240000000001</v>
       </c>
       <c r="G17">
         <v>207.8</v>
@@ -2809,28 +2809,28 @@
         <v>737.8</v>
       </c>
       <c r="M17">
-        <v>37.7544255</v>
+        <v>40.27138720000001</v>
       </c>
       <c r="N17">
-        <v>700.0455744999999</v>
+        <v>697.5286127999999</v>
       </c>
       <c r="O17">
-        <v>63.00410170499999</v>
+        <v>62.77757515199999</v>
       </c>
       <c r="P17">
-        <v>637.0414727949999</v>
+        <v>634.751037648</v>
       </c>
       <c r="Q17">
-        <v>763.841472795</v>
+        <v>761.551037648</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1163167251527499</v>
+        <v>0.1170911105446959</v>
       </c>
       <c r="T17">
-        <v>1.026104272988873</v>
+        <v>1.037372524001591</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.54207990795675</v>
+        <v>18.32069991370945</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1056802128575445</v>
+        <v>0.1056252593352518</v>
       </c>
       <c r="C18">
-        <v>4323.505046821544</v>
+        <v>4277.982025538146</v>
       </c>
       <c r="D18">
-        <v>4916.329046821544</v>
+        <v>4920.845025538146</v>
       </c>
       <c r="E18">
-        <v>561.8240000000001</v>
+        <v>611.8630000000001</v>
       </c>
       <c r="F18">
-        <v>800.6240000000001</v>
+        <v>850.6630000000001</v>
       </c>
       <c r="G18">
         <v>207.8</v>
@@ -2891,28 +2891,28 @@
         <v>737.8</v>
       </c>
       <c r="M18">
-        <v>40.27138720000001</v>
+        <v>42.7883489</v>
       </c>
       <c r="N18">
-        <v>697.5286127999999</v>
+        <v>695.0116511</v>
       </c>
       <c r="O18">
-        <v>62.77757515199999</v>
+        <v>62.551048599</v>
       </c>
       <c r="P18">
-        <v>634.751037648</v>
+        <v>632.460602501</v>
       </c>
       <c r="Q18">
-        <v>761.551037648</v>
+        <v>759.2606025010001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1170911105446959</v>
+        <v>0.1178841558256045</v>
       </c>
       <c r="T18">
-        <v>1.037372524001591</v>
+        <v>1.048912299135097</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.32069991370945</v>
+        <v>17.24301168349125</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1056252593352518</v>
+        <v>0.105570305812959</v>
       </c>
       <c r="C19">
-        <v>4277.982025538146</v>
+        <v>4232.467308342663</v>
       </c>
       <c r="D19">
-        <v>4920.845025538146</v>
+        <v>4925.369308342663</v>
       </c>
       <c r="E19">
-        <v>611.8630000000001</v>
+        <v>661.9020000000003</v>
       </c>
       <c r="F19">
-        <v>850.6630000000001</v>
+        <v>900.7020000000002</v>
       </c>
       <c r="G19">
         <v>207.8</v>
@@ -2973,28 +2973,28 @@
         <v>737.8</v>
       </c>
       <c r="M19">
-        <v>42.7883489</v>
+        <v>45.30531060000001</v>
       </c>
       <c r="N19">
-        <v>695.0116511</v>
+        <v>692.4946894</v>
       </c>
       <c r="O19">
-        <v>62.551048599</v>
+        <v>62.324522046</v>
       </c>
       <c r="P19">
-        <v>632.460602501</v>
+        <v>630.170167354</v>
       </c>
       <c r="Q19">
-        <v>759.2606025010001</v>
+        <v>756.9701673540001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1178841558256045</v>
+        <v>0.1186965436743402</v>
       </c>
       <c r="T19">
-        <v>1.048912299135097</v>
+        <v>1.060733532198689</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.24301168349125</v>
+        <v>16.28506658996395</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.105570305812959</v>
+        <v>0.1055153522906661</v>
       </c>
       <c r="C20">
-        <v>4232.467308342662</v>
+        <v>4186.960918160805</v>
       </c>
       <c r="D20">
-        <v>4925.369308342662</v>
+        <v>4929.901918160805</v>
       </c>
       <c r="E20">
-        <v>661.902</v>
+        <v>711.941</v>
       </c>
       <c r="F20">
-        <v>900.7020000000001</v>
+        <v>950.7410000000001</v>
       </c>
       <c r="G20">
         <v>207.8</v>
@@ -3055,28 +3055,28 @@
         <v>737.8</v>
       </c>
       <c r="M20">
-        <v>45.30531060000001</v>
+        <v>47.8222723</v>
       </c>
       <c r="N20">
-        <v>692.4946894</v>
+        <v>689.9777276999999</v>
       </c>
       <c r="O20">
-        <v>62.324522046</v>
+        <v>62.09799549299999</v>
       </c>
       <c r="P20">
-        <v>630.170167354</v>
+        <v>627.879732207</v>
       </c>
       <c r="Q20">
-        <v>756.9701673540001</v>
+        <v>754.679732207</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1186965436743402</v>
+        <v>0.1195289904823039</v>
       </c>
       <c r="T20">
-        <v>1.060733532198689</v>
+        <v>1.072846647560147</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.28506658996395</v>
+        <v>15.42795782207112</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1055153522906661</v>
+        <v>0.1054603987683734</v>
       </c>
       <c r="C21">
-        <v>4186.960918160805</v>
+        <v>4141.462878002736</v>
       </c>
       <c r="D21">
-        <v>4929.901918160805</v>
+        <v>4934.442878002736</v>
       </c>
       <c r="E21">
-        <v>711.941</v>
+        <v>761.9800000000002</v>
       </c>
       <c r="F21">
-        <v>950.7410000000001</v>
+        <v>1000.78</v>
       </c>
       <c r="G21">
         <v>207.8</v>
@@ -3137,28 +3137,28 @@
         <v>737.8</v>
       </c>
       <c r="M21">
-        <v>47.8222723</v>
+        <v>50.339234</v>
       </c>
       <c r="N21">
-        <v>689.9777276999999</v>
+        <v>687.4607659999999</v>
       </c>
       <c r="O21">
-        <v>62.09799549299999</v>
+        <v>61.87146893999999</v>
       </c>
       <c r="P21">
-        <v>627.879732207</v>
+        <v>625.5892970599999</v>
       </c>
       <c r="Q21">
-        <v>754.679732207</v>
+        <v>752.38929706</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1195289904823039</v>
+        <v>0.1203822484604667</v>
       </c>
       <c r="T21">
-        <v>1.072846647560147</v>
+        <v>1.085262590805642</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.42795782207112</v>
+        <v>14.65655993096756</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1054603987683734</v>
+        <v>0.1054054452460805</v>
       </c>
       <c r="C22">
-        <v>4141.462878002736</v>
+        <v>4095.9732109635</v>
       </c>
       <c r="D22">
-        <v>4934.442878002736</v>
+        <v>4938.9922109635</v>
       </c>
       <c r="E22">
-        <v>761.9800000000002</v>
+        <v>812.0190000000002</v>
       </c>
       <c r="F22">
-        <v>1000.78</v>
+        <v>1050.819</v>
       </c>
       <c r="G22">
         <v>207.8</v>
@@ -3219,28 +3219,28 @@
         <v>737.8</v>
       </c>
       <c r="M22">
-        <v>50.339234</v>
+        <v>52.85619570000001</v>
       </c>
       <c r="N22">
-        <v>687.4607659999999</v>
+        <v>684.9438042999999</v>
       </c>
       <c r="O22">
-        <v>61.87146893999999</v>
+        <v>61.64494238699999</v>
       </c>
       <c r="P22">
-        <v>625.5892970599999</v>
+        <v>623.2988619129999</v>
       </c>
       <c r="Q22">
-        <v>752.38929706</v>
+        <v>750.098861913</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1203822484604667</v>
+        <v>0.121257107906431</v>
       </c>
       <c r="T22">
-        <v>1.085262590805642</v>
+        <v>1.097992861728238</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.65655993096756</v>
+        <v>13.95862850568339</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1054054452460805</v>
+        <v>0.1053504917237877</v>
       </c>
       <c r="C23">
-        <v>4095.9732109635</v>
+        <v>4050.49194022337</v>
       </c>
       <c r="D23">
-        <v>4938.9922109635</v>
+        <v>4943.54994022337</v>
       </c>
       <c r="E23">
-        <v>812.0190000000002</v>
+        <v>862.0580000000002</v>
       </c>
       <c r="F23">
-        <v>1050.819</v>
+        <v>1100.858</v>
       </c>
       <c r="G23">
         <v>207.8</v>
@@ -3301,28 +3301,28 @@
         <v>737.8</v>
       </c>
       <c r="M23">
-        <v>52.85619570000001</v>
+        <v>55.3731574</v>
       </c>
       <c r="N23">
-        <v>684.9438042999999</v>
+        <v>682.4268426</v>
       </c>
       <c r="O23">
-        <v>61.64494238699999</v>
+        <v>61.41841583399999</v>
       </c>
       <c r="P23">
-        <v>623.2988619129999</v>
+        <v>621.008426766</v>
       </c>
       <c r="Q23">
-        <v>750.098861913</v>
+        <v>747.808426766</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.121257107906431</v>
+        <v>0.1221543996458817</v>
       </c>
       <c r="T23">
-        <v>1.097992861728238</v>
+        <v>1.111049549853977</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.95862850568339</v>
+        <v>13.32414539178869</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1053504917237877</v>
+        <v>0.1056094882014949</v>
       </c>
       <c r="C24">
-        <v>4050.49194022337</v>
+        <v>3979.045600679283</v>
       </c>
       <c r="D24">
-        <v>4943.54994022337</v>
+        <v>4922.142600679283</v>
       </c>
       <c r="E24">
-        <v>862.0580000000002</v>
+        <v>912.0970000000002</v>
       </c>
       <c r="F24">
-        <v>1100.858</v>
+        <v>1150.897</v>
       </c>
       <c r="G24">
         <v>207.8</v>
@@ -3383,45 +3383,45 @@
         <v>737.8</v>
       </c>
       <c r="M24">
-        <v>55.3731574</v>
+        <v>59.61646460000001</v>
       </c>
       <c r="N24">
-        <v>682.4268426</v>
+        <v>678.1835354</v>
       </c>
       <c r="O24">
-        <v>61.41841583399999</v>
+        <v>61.036518186</v>
       </c>
       <c r="P24">
-        <v>621.008426766</v>
+        <v>617.147017214</v>
       </c>
       <c r="Q24">
-        <v>747.808426766</v>
+        <v>743.9470172140001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1221543996458817</v>
+        <v>0.1230749976642791</v>
       </c>
       <c r="T24">
-        <v>1.111049549853977</v>
+        <v>1.124445372736229</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.09</v>
       </c>
       <c r="W24">
-        <v>0.045773</v>
+        <v>0.047138</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.32414539178869</v>
+        <v>12.37577580204244</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1056094882014949</v>
+        <v>0.1055681846792021</v>
       </c>
       <c r="C25">
-        <v>3979.045600679283</v>
+        <v>3932.408106475832</v>
       </c>
       <c r="D25">
-        <v>4922.142600679283</v>
+        <v>4925.544106475832</v>
       </c>
       <c r="E25">
-        <v>912.0970000000002</v>
+        <v>962.1360000000002</v>
       </c>
       <c r="F25">
-        <v>1150.897</v>
+        <v>1200.936</v>
       </c>
       <c r="G25">
         <v>207.8</v>
@@ -3465,28 +3465,28 @@
         <v>737.8</v>
       </c>
       <c r="M25">
-        <v>59.61646460000001</v>
+        <v>62.20848480000001</v>
       </c>
       <c r="N25">
-        <v>678.1835354</v>
+        <v>675.5915152</v>
       </c>
       <c r="O25">
-        <v>61.036518186</v>
+        <v>60.803236368</v>
       </c>
       <c r="P25">
-        <v>617.147017214</v>
+        <v>614.7882788320001</v>
       </c>
       <c r="Q25">
-        <v>743.9470172140001</v>
+        <v>741.5882788320001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1230749976642791</v>
+        <v>0.1240198219463186</v>
       </c>
       <c r="T25">
-        <v>1.124445372736229</v>
+        <v>1.138193717273277</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.37577580204244</v>
+        <v>11.86011847695734</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1055681846792021</v>
+        <v>0.1055268811569093</v>
       </c>
       <c r="C26">
-        <v>3932.408106475832</v>
+        <v>3885.775316826439</v>
       </c>
       <c r="D26">
-        <v>4925.544106475832</v>
+        <v>4928.950316826439</v>
       </c>
       <c r="E26">
-        <v>962.1360000000002</v>
+        <v>1012.175</v>
       </c>
       <c r="F26">
-        <v>1200.936</v>
+        <v>1250.975</v>
       </c>
       <c r="G26">
         <v>207.8</v>
@@ -3547,28 +3547,28 @@
         <v>737.8</v>
       </c>
       <c r="M26">
-        <v>62.20848480000001</v>
+        <v>64.800505</v>
       </c>
       <c r="N26">
-        <v>675.5915152</v>
+        <v>672.9994949999999</v>
       </c>
       <c r="O26">
-        <v>60.803236368</v>
+        <v>60.56995454999999</v>
       </c>
       <c r="P26">
-        <v>614.7882788320001</v>
+        <v>612.4295404499999</v>
       </c>
       <c r="Q26">
-        <v>741.5882788320001</v>
+        <v>739.2295404499999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1240198219463186</v>
+        <v>0.1249898415425457</v>
       </c>
       <c r="T26">
-        <v>1.138193717273277</v>
+        <v>1.152308684331313</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.86011847695734</v>
+        <v>11.38571373787905</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1055268811569093</v>
+        <v>0.1054855776346165</v>
       </c>
       <c r="C27">
-        <v>3885.775316826439</v>
+        <v>3839.147241498015</v>
       </c>
       <c r="D27">
-        <v>4928.950316826439</v>
+        <v>4932.361241498015</v>
       </c>
       <c r="E27">
-        <v>1012.175</v>
+        <v>1062.214</v>
       </c>
       <c r="F27">
-        <v>1250.975</v>
+        <v>1301.014</v>
       </c>
       <c r="G27">
         <v>207.8</v>
@@ -3629,28 +3629,28 @@
         <v>737.8</v>
       </c>
       <c r="M27">
-        <v>64.800505</v>
+        <v>67.39252520000001</v>
       </c>
       <c r="N27">
-        <v>672.9994949999999</v>
+        <v>670.4074747999999</v>
       </c>
       <c r="O27">
-        <v>60.56995454999999</v>
+        <v>60.33667273199999</v>
       </c>
       <c r="P27">
-        <v>612.4295404499999</v>
+        <v>610.0708020679999</v>
       </c>
       <c r="Q27">
-        <v>739.2295404499999</v>
+        <v>736.870802068</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1249898415425457</v>
+        <v>0.1259860778846169</v>
       </c>
       <c r="T27">
-        <v>1.152308684331313</v>
+        <v>1.166805136985512</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.38571373787905</v>
+        <v>10.94780167103755</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1054855776346165</v>
+        <v>0.1054442741123237</v>
       </c>
       <c r="C28">
-        <v>3839.147241498015</v>
+        <v>3792.523890284529</v>
       </c>
       <c r="D28">
-        <v>4932.361241498015</v>
+        <v>4935.776890284529</v>
       </c>
       <c r="E28">
-        <v>1062.214</v>
+        <v>1112.253</v>
       </c>
       <c r="F28">
-        <v>1301.014</v>
+        <v>1351.053</v>
       </c>
       <c r="G28">
         <v>207.8</v>
@@ -3711,28 +3711,28 @@
         <v>737.8</v>
       </c>
       <c r="M28">
-        <v>67.39252520000001</v>
+        <v>69.98454540000002</v>
       </c>
       <c r="N28">
-        <v>670.4074747999999</v>
+        <v>667.8154546</v>
       </c>
       <c r="O28">
-        <v>60.33667273199999</v>
+        <v>60.10339091399999</v>
       </c>
       <c r="P28">
-        <v>610.0708020679999</v>
+        <v>607.712063686</v>
       </c>
       <c r="Q28">
-        <v>736.870802068</v>
+        <v>734.512063686</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1259860778846169</v>
+        <v>0.1270096083730462</v>
       </c>
       <c r="T28">
-        <v>1.166805136985512</v>
+        <v>1.181698752726128</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.94780167103755</v>
+        <v>10.54232753507319</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1054442741123237</v>
+        <v>0.1054029705900309</v>
       </c>
       <c r="C29">
-        <v>3792.523890284529</v>
+        <v>3745.905273007104</v>
       </c>
       <c r="D29">
-        <v>4935.776890284529</v>
+        <v>4939.197273007105</v>
       </c>
       <c r="E29">
-        <v>1112.253</v>
+        <v>1162.292</v>
       </c>
       <c r="F29">
-        <v>1351.053</v>
+        <v>1401.092</v>
       </c>
       <c r="G29">
         <v>207.8</v>
@@ -3793,28 +3793,28 @@
         <v>737.8</v>
       </c>
       <c r="M29">
-        <v>69.98454540000002</v>
+        <v>72.57656560000001</v>
       </c>
       <c r="N29">
-        <v>667.8154546</v>
+        <v>665.2234344</v>
       </c>
       <c r="O29">
-        <v>60.10339091399999</v>
+        <v>59.87010909599999</v>
       </c>
       <c r="P29">
-        <v>607.712063686</v>
+        <v>605.353325304</v>
       </c>
       <c r="Q29">
-        <v>734.512063686</v>
+        <v>732.1533253040001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1270096083730462</v>
+        <v>0.1280615702639318</v>
       </c>
       <c r="T29">
-        <v>1.181698752726128</v>
+        <v>1.197006080015094</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.54232753507319</v>
+        <v>10.16581583739201</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1054029705900309</v>
+        <v>0.1053616670677381</v>
       </c>
       <c r="C30">
-        <v>3745.905273007104</v>
+        <v>3699.291399514093</v>
       </c>
       <c r="D30">
-        <v>4939.197273007105</v>
+        <v>4942.622399514093</v>
       </c>
       <c r="E30">
-        <v>1162.292</v>
+        <v>1212.331</v>
       </c>
       <c r="F30">
-        <v>1401.092</v>
+        <v>1451.131</v>
       </c>
       <c r="G30">
         <v>207.8</v>
@@ -3875,28 +3875,28 @@
         <v>737.8</v>
       </c>
       <c r="M30">
-        <v>72.57656560000001</v>
+        <v>75.16858580000002</v>
       </c>
       <c r="N30">
-        <v>665.2234344</v>
+        <v>662.6314141999999</v>
       </c>
       <c r="O30">
-        <v>59.87010909599999</v>
+        <v>59.63682727799998</v>
       </c>
       <c r="P30">
-        <v>605.353325304</v>
+        <v>602.9945869219999</v>
       </c>
       <c r="Q30">
-        <v>732.1533253040001</v>
+        <v>729.794586922</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1280615702639318</v>
+        <v>0.1291431648841382</v>
       </c>
       <c r="T30">
-        <v>1.197006080015094</v>
+        <v>1.212744599622059</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.16581583739201</v>
+        <v>9.815270463688831</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1053616670677381</v>
+        <v>0.1057844635454453</v>
       </c>
       <c r="C31">
-        <v>3699.291399514093</v>
+        <v>3614.414656244654</v>
       </c>
       <c r="D31">
-        <v>4942.622399514093</v>
+        <v>4907.784656244654</v>
       </c>
       <c r="E31">
-        <v>1212.331</v>
+        <v>1262.37</v>
       </c>
       <c r="F31">
-        <v>1451.131</v>
+        <v>1501.17</v>
       </c>
       <c r="G31">
         <v>207.8</v>
@@ -3957,45 +3957,45 @@
         <v>737.8</v>
       </c>
       <c r="M31">
-        <v>75.1685858</v>
+        <v>80.312595</v>
       </c>
       <c r="N31">
-        <v>662.6314142</v>
+        <v>657.487405</v>
       </c>
       <c r="O31">
-        <v>59.636827278</v>
+        <v>59.17386644999999</v>
       </c>
       <c r="P31">
-        <v>602.9945869220001</v>
+        <v>598.31353855</v>
       </c>
       <c r="Q31">
-        <v>729.7945869220001</v>
+        <v>725.11353855</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1291431648841382</v>
+        <v>0.130255662207779</v>
       </c>
       <c r="T31">
-        <v>1.212744599622059</v>
+        <v>1.228932791217794</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.09</v>
       </c>
       <c r="W31">
-        <v>0.047138</v>
+        <v>0.048685</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>9.815270463688835</v>
+        <v>9.186603919347892</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1057844635454453</v>
+        <v>0.1057586300231525</v>
       </c>
       <c r="C32">
-        <v>3614.414656244654</v>
+        <v>3566.490203629685</v>
       </c>
       <c r="D32">
-        <v>4907.784656244654</v>
+        <v>4909.899203629685</v>
       </c>
       <c r="E32">
-        <v>1262.37</v>
+        <v>1312.409</v>
       </c>
       <c r="F32">
-        <v>1501.17</v>
+        <v>1551.209</v>
       </c>
       <c r="G32">
         <v>207.8</v>
@@ -4039,28 +4039,28 @@
         <v>737.8</v>
       </c>
       <c r="M32">
-        <v>80.312595</v>
+        <v>82.9896815</v>
       </c>
       <c r="N32">
-        <v>657.487405</v>
+        <v>654.8103185</v>
       </c>
       <c r="O32">
-        <v>59.17386644999999</v>
+        <v>58.932928665</v>
       </c>
       <c r="P32">
-        <v>598.31353855</v>
+        <v>595.877389835</v>
       </c>
       <c r="Q32">
-        <v>725.11353855</v>
+        <v>722.6773898350001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.130255662207779</v>
+        <v>0.1314004058306557</v>
       </c>
       <c r="T32">
-        <v>1.228932791217794</v>
+        <v>1.245590205758333</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.186603919347892</v>
+        <v>8.890261857433444</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1057586300231525</v>
+        <v>0.1057327965008597</v>
       </c>
       <c r="C33">
-        <v>3566.490203629685</v>
+        <v>3518.567573930051</v>
       </c>
       <c r="D33">
-        <v>4909.899203629685</v>
+        <v>4912.015573930052</v>
       </c>
       <c r="E33">
-        <v>1312.409</v>
+        <v>1362.448</v>
       </c>
       <c r="F33">
-        <v>1551.209</v>
+        <v>1601.248</v>
       </c>
       <c r="G33">
         <v>207.8</v>
@@ -4121,28 +4121,28 @@
         <v>737.8</v>
       </c>
       <c r="M33">
-        <v>82.9896815</v>
+        <v>85.66676800000002</v>
       </c>
       <c r="N33">
-        <v>654.8103185</v>
+        <v>652.1332319999999</v>
       </c>
       <c r="O33">
-        <v>58.932928665</v>
+        <v>58.69199087999999</v>
       </c>
       <c r="P33">
-        <v>595.877389835</v>
+        <v>593.4412411199999</v>
       </c>
       <c r="Q33">
-        <v>722.6773898350001</v>
+        <v>720.2412411199999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1314004058306557</v>
+        <v>0.1325788183836172</v>
       </c>
       <c r="T33">
-        <v>1.245590205758333</v>
+        <v>1.262737544255948</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.890261857433444</v>
+        <v>8.612441174388646</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1057327965008597</v>
+        <v>0.1057069629785668</v>
       </c>
       <c r="C34">
-        <v>3518.567573930051</v>
+        <v>3470.646769504032</v>
       </c>
       <c r="D34">
-        <v>4912.015573930052</v>
+        <v>4914.133769504032</v>
       </c>
       <c r="E34">
-        <v>1362.448</v>
+        <v>1412.487</v>
       </c>
       <c r="F34">
-        <v>1601.248</v>
+        <v>1651.287</v>
       </c>
       <c r="G34">
         <v>207.8</v>
@@ -4203,28 +4203,28 @@
         <v>737.8</v>
       </c>
       <c r="M34">
-        <v>85.66676800000002</v>
+        <v>88.34385450000001</v>
       </c>
       <c r="N34">
-        <v>652.1332319999999</v>
+        <v>649.4561454999999</v>
       </c>
       <c r="O34">
-        <v>58.69199087999999</v>
+        <v>58.45105309499999</v>
       </c>
       <c r="P34">
-        <v>593.4412411199999</v>
+        <v>591.0050924049999</v>
       </c>
       <c r="Q34">
-        <v>720.2412411199999</v>
+        <v>717.805092405</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1325788183836172</v>
+        <v>0.1337924074306968</v>
       </c>
       <c r="T34">
-        <v>1.262737544255948</v>
+        <v>1.280396743604237</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.612441174388646</v>
+        <v>8.351458108498083</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1057069629785668</v>
+        <v>0.1056811294562741</v>
       </c>
       <c r="C35">
-        <v>3470.646769504032</v>
+        <v>3422.727792713963</v>
       </c>
       <c r="D35">
-        <v>4914.133769504032</v>
+        <v>4916.253792713963</v>
       </c>
       <c r="E35">
-        <v>1412.487</v>
+        <v>1462.526</v>
       </c>
       <c r="F35">
-        <v>1651.287</v>
+        <v>1701.326</v>
       </c>
       <c r="G35">
         <v>207.8</v>
@@ -4285,28 +4285,28 @@
         <v>737.8</v>
       </c>
       <c r="M35">
-        <v>88.34385450000001</v>
+        <v>91.02094100000001</v>
       </c>
       <c r="N35">
-        <v>649.4561454999999</v>
+        <v>646.779059</v>
       </c>
       <c r="O35">
-        <v>58.45105309499999</v>
+        <v>58.21011530999999</v>
       </c>
       <c r="P35">
-        <v>591.0050924049999</v>
+        <v>588.56894369</v>
       </c>
       <c r="Q35">
-        <v>717.805092405</v>
+        <v>715.36894369</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1337924074306968</v>
+        <v>0.1350427719034455</v>
       </c>
       <c r="T35">
-        <v>1.280396743604237</v>
+        <v>1.298591070205505</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.351458108498083</v>
+        <v>8.105826987659905</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1056811294562741</v>
+        <v>0.1056552959339812</v>
       </c>
       <c r="C36">
-        <v>3422.727792713963</v>
+        <v>3374.810645926272</v>
       </c>
       <c r="D36">
-        <v>4916.253792713963</v>
+        <v>4918.375645926272</v>
       </c>
       <c r="E36">
-        <v>1462.526</v>
+        <v>1512.565000000001</v>
       </c>
       <c r="F36">
-        <v>1701.326</v>
+        <v>1751.365</v>
       </c>
       <c r="G36">
         <v>207.8</v>
@@ -4367,28 +4367,28 @@
         <v>737.8</v>
       </c>
       <c r="M36">
-        <v>91.02094100000001</v>
+        <v>93.69802750000002</v>
       </c>
       <c r="N36">
-        <v>646.779059</v>
+        <v>644.1019724999999</v>
       </c>
       <c r="O36">
-        <v>58.21011530999999</v>
+        <v>57.96917752499998</v>
       </c>
       <c r="P36">
-        <v>588.56894369</v>
+        <v>586.1327949749999</v>
       </c>
       <c r="Q36">
-        <v>715.36894369</v>
+        <v>712.932794975</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1350427719034455</v>
+        <v>0.1363316091292019</v>
       </c>
       <c r="T36">
-        <v>1.298591070205505</v>
+        <v>1.317345222240657</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.105826987659905</v>
+        <v>7.87423193086962</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1056552959339812</v>
+        <v>0.1056294624116884</v>
       </c>
       <c r="C37">
-        <v>3374.810645926272</v>
+        <v>3326.895331511462</v>
       </c>
       <c r="D37">
-        <v>4918.375645926272</v>
+        <v>4920.499331511463</v>
       </c>
       <c r="E37">
-        <v>1512.565000000001</v>
+        <v>1562.604</v>
       </c>
       <c r="F37">
-        <v>1751.365</v>
+        <v>1801.404</v>
       </c>
       <c r="G37">
         <v>207.8</v>
@@ -4449,28 +4449,28 @@
         <v>737.8</v>
       </c>
       <c r="M37">
-        <v>93.69802750000002</v>
+        <v>96.37511400000002</v>
       </c>
       <c r="N37">
-        <v>644.1019724999999</v>
+        <v>641.4248859999999</v>
       </c>
       <c r="O37">
-        <v>57.96917752499998</v>
+        <v>57.72823973999999</v>
       </c>
       <c r="P37">
-        <v>586.1327949749999</v>
+        <v>583.6966462599999</v>
       </c>
       <c r="Q37">
-        <v>712.932794975</v>
+        <v>710.4966462599999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1363316091292019</v>
+        <v>0.1376607225182632</v>
       </c>
       <c r="T37">
-        <v>1.317345222240657</v>
+        <v>1.336685441526908</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.87423193086962</v>
+        <v>7.655503266123241</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1056294624116884</v>
+        <v>0.1058729888893956</v>
       </c>
       <c r="C38">
-        <v>3326.895331511463</v>
+        <v>3256.9093987399</v>
       </c>
       <c r="D38">
-        <v>4920.499331511463</v>
+        <v>4900.5523987399</v>
       </c>
       <c r="E38">
-        <v>1562.604</v>
+        <v>1612.643</v>
       </c>
       <c r="F38">
-        <v>1801.404</v>
+        <v>1851.443</v>
       </c>
       <c r="G38">
         <v>207.8</v>
@@ -4531,45 +4531,45 @@
         <v>737.8</v>
       </c>
       <c r="M38">
-        <v>96.37511400000001</v>
+        <v>100.5333549</v>
       </c>
       <c r="N38">
-        <v>641.4248859999999</v>
+        <v>637.2666450999999</v>
       </c>
       <c r="O38">
-        <v>57.72823973999999</v>
+        <v>57.35399805899999</v>
       </c>
       <c r="P38">
-        <v>583.6966462599999</v>
+        <v>579.9126470409999</v>
       </c>
       <c r="Q38">
-        <v>710.4966462599999</v>
+        <v>706.712647041</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1376607225182632</v>
+        <v>0.1390320299831677</v>
       </c>
       <c r="T38">
-        <v>1.336685441526908</v>
+        <v>1.356639636028596</v>
       </c>
       <c r="U38">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V38">
         <v>0.09</v>
       </c>
       <c r="W38">
-        <v>0.048685</v>
+        <v>0.04941300000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y38">
-        <v>7.655503266123242</v>
+        <v>7.338857842095149</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1058729888893956</v>
+        <v>0.1058544353671028</v>
       </c>
       <c r="C39">
-        <v>3256.9093987399</v>
+        <v>3208.384400289017</v>
       </c>
       <c r="D39">
-        <v>4900.5523987399</v>
+        <v>4902.066400289017</v>
       </c>
       <c r="E39">
-        <v>1612.643</v>
+        <v>1662.682</v>
       </c>
       <c r="F39">
-        <v>1851.443</v>
+        <v>1901.482</v>
       </c>
       <c r="G39">
         <v>207.8</v>
@@ -4613,28 +4613,28 @@
         <v>737.8</v>
       </c>
       <c r="M39">
-        <v>100.5333549</v>
+        <v>103.2504726</v>
       </c>
       <c r="N39">
-        <v>637.2666450999999</v>
+        <v>634.5495274</v>
       </c>
       <c r="O39">
-        <v>57.35399805899999</v>
+        <v>57.10945746599999</v>
       </c>
       <c r="P39">
-        <v>579.9126470409999</v>
+        <v>577.440069934</v>
       </c>
       <c r="Q39">
-        <v>706.712647041</v>
+        <v>704.2400699340001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1390320299831677</v>
+        <v>0.1404475731727465</v>
       </c>
       <c r="T39">
-        <v>1.356639636028596</v>
+        <v>1.377237514223887</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.338857842095149</v>
+        <v>7.145730004145278</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1058544353671028</v>
+        <v>0.10583588184481</v>
       </c>
       <c r="C40">
-        <v>3208.384400289017</v>
+        <v>3159.860337613894</v>
       </c>
       <c r="D40">
-        <v>4902.066400289017</v>
+        <v>4903.581337613894</v>
       </c>
       <c r="E40">
-        <v>1662.682</v>
+        <v>1712.721</v>
       </c>
       <c r="F40">
-        <v>1901.482</v>
+        <v>1951.521</v>
       </c>
       <c r="G40">
         <v>207.8</v>
@@ -4695,28 +4695,28 @@
         <v>737.8</v>
       </c>
       <c r="M40">
-        <v>103.2504726</v>
+        <v>105.9675903</v>
       </c>
       <c r="N40">
-        <v>634.5495274</v>
+        <v>631.8324097</v>
       </c>
       <c r="O40">
-        <v>57.10945746599999</v>
+        <v>56.864916873</v>
       </c>
       <c r="P40">
-        <v>577.440069934</v>
+        <v>574.967492827</v>
       </c>
       <c r="Q40">
-        <v>704.2400699340001</v>
+        <v>701.7674928270001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1404475731727465</v>
+        <v>0.1419095276144426</v>
       </c>
       <c r="T40">
-        <v>1.377237514223887</v>
+        <v>1.398510732687875</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.145730004145278</v>
+        <v>6.962506157885143</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.10583588184481</v>
+        <v>0.1058173283225172</v>
       </c>
       <c r="C41">
-        <v>3159.860337613894</v>
+        <v>3111.337211582375</v>
       </c>
       <c r="D41">
-        <v>4903.581337613894</v>
+        <v>4905.097211582375</v>
       </c>
       <c r="E41">
-        <v>1712.721</v>
+        <v>1762.76</v>
       </c>
       <c r="F41">
-        <v>1951.521</v>
+        <v>2001.56</v>
       </c>
       <c r="G41">
         <v>207.8</v>
@@ -4777,28 +4777,28 @@
         <v>737.8</v>
       </c>
       <c r="M41">
-        <v>105.9675903</v>
+        <v>108.684708</v>
       </c>
       <c r="N41">
-        <v>631.8324097</v>
+        <v>629.115292</v>
       </c>
       <c r="O41">
-        <v>56.864916873</v>
+        <v>56.62037628</v>
       </c>
       <c r="P41">
-        <v>574.967492827</v>
+        <v>572.49491572</v>
       </c>
       <c r="Q41">
-        <v>701.7674928270001</v>
+        <v>699.2949157200001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1419095276144426</v>
+        <v>0.143420213870862</v>
       </c>
       <c r="T41">
-        <v>1.398510732687875</v>
+        <v>1.420493058433997</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.962506157885143</v>
+        <v>6.788443503938013</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1058173283225172</v>
+        <v>0.1057987748002244</v>
       </c>
       <c r="C42">
-        <v>3111.337211582375</v>
+        <v>3062.815023063386</v>
       </c>
       <c r="D42">
-        <v>4905.097211582375</v>
+        <v>4906.614023063386</v>
       </c>
       <c r="E42">
-        <v>1762.76</v>
+        <v>1812.799</v>
       </c>
       <c r="F42">
-        <v>2001.56</v>
+        <v>2051.599</v>
       </c>
       <c r="G42">
         <v>207.8</v>
@@ -4859,28 +4859,28 @@
         <v>737.8</v>
       </c>
       <c r="M42">
-        <v>108.684708</v>
+        <v>111.4018257</v>
       </c>
       <c r="N42">
-        <v>629.115292</v>
+        <v>626.3981742999999</v>
       </c>
       <c r="O42">
-        <v>56.62037628</v>
+        <v>56.37583568699999</v>
       </c>
       <c r="P42">
-        <v>572.49491572</v>
+        <v>570.022338613</v>
       </c>
       <c r="Q42">
-        <v>699.2949157200001</v>
+        <v>696.8223386130001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.143420213870862</v>
+        <v>0.1449821098308888</v>
       </c>
       <c r="T42">
-        <v>1.420493058433997</v>
+        <v>1.443220547764733</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.788443503938013</v>
+        <v>6.622871711159037</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1057987748002244</v>
+        <v>0.1057802212779316</v>
       </c>
       <c r="C43">
-        <v>3062.815023063386</v>
+        <v>3014.293772926915</v>
       </c>
       <c r="D43">
-        <v>4906.614023063386</v>
+        <v>4908.131772926915</v>
       </c>
       <c r="E43">
-        <v>1812.799</v>
+        <v>1862.838</v>
       </c>
       <c r="F43">
-        <v>2051.599</v>
+        <v>2101.638</v>
       </c>
       <c r="G43">
         <v>207.8</v>
@@ -4941,28 +4941,28 @@
         <v>737.8</v>
       </c>
       <c r="M43">
-        <v>111.4018257</v>
+        <v>114.1189434</v>
       </c>
       <c r="N43">
-        <v>626.3981742999999</v>
+        <v>623.6810565999999</v>
       </c>
       <c r="O43">
-        <v>56.37583568699999</v>
+        <v>56.13129509399999</v>
       </c>
       <c r="P43">
-        <v>570.022338613</v>
+        <v>567.549761506</v>
       </c>
       <c r="Q43">
-        <v>696.8223386130001</v>
+        <v>694.349761506</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1449821098308888</v>
+        <v>0.1465978642722959</v>
       </c>
       <c r="T43">
-        <v>1.443220547764733</v>
+        <v>1.466731743624115</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.622871711159037</v>
+        <v>6.465184289464775</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1057802212779316</v>
+        <v>0.1057616677556388</v>
       </c>
       <c r="C44">
-        <v>3014.293772926914</v>
+        <v>2965.773462044037</v>
       </c>
       <c r="D44">
-        <v>4908.131772926914</v>
+        <v>4909.650462044037</v>
       </c>
       <c r="E44">
-        <v>1862.838</v>
+        <v>1912.877</v>
       </c>
       <c r="F44">
-        <v>2101.638</v>
+        <v>2151.677</v>
       </c>
       <c r="G44">
         <v>207.8</v>
@@ -5023,28 +5023,28 @@
         <v>737.8</v>
       </c>
       <c r="M44">
-        <v>114.1189434</v>
+        <v>116.8360611</v>
       </c>
       <c r="N44">
-        <v>623.6810565999999</v>
+        <v>620.9639388999999</v>
       </c>
       <c r="O44">
-        <v>56.13129509399999</v>
+        <v>55.88675450099999</v>
       </c>
       <c r="P44">
-        <v>567.549761506</v>
+        <v>565.0771843989999</v>
       </c>
       <c r="Q44">
-        <v>694.349761506</v>
+        <v>691.8771843989999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1465978642722959</v>
+        <v>0.1482703118519979</v>
       </c>
       <c r="T44">
-        <v>1.466731743624115</v>
+        <v>1.491067893724177</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.465184289464775</v>
+        <v>6.314831166453966</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1057616677556388</v>
+        <v>0.105743114233346</v>
       </c>
       <c r="C45">
-        <v>2965.773462044037</v>
+        <v>2917.254091286904</v>
       </c>
       <c r="D45">
-        <v>4909.650462044037</v>
+        <v>4911.170091286904</v>
       </c>
       <c r="E45">
-        <v>1912.877</v>
+        <v>1962.916</v>
       </c>
       <c r="F45">
-        <v>2151.677</v>
+        <v>2201.716</v>
       </c>
       <c r="G45">
         <v>207.8</v>
@@ -5105,28 +5105,28 @@
         <v>737.8</v>
       </c>
       <c r="M45">
-        <v>116.8360611</v>
+        <v>119.5531788</v>
       </c>
       <c r="N45">
-        <v>620.9639388999999</v>
+        <v>618.2468211999999</v>
       </c>
       <c r="O45">
-        <v>55.88675450099999</v>
+        <v>55.64221390799999</v>
       </c>
       <c r="P45">
-        <v>565.0771843989999</v>
+        <v>562.6046072919999</v>
       </c>
       <c r="Q45">
-        <v>691.8771843989999</v>
+        <v>689.4046072919999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1482703118519979</v>
+        <v>0.1500024897024035</v>
       </c>
       <c r="T45">
-        <v>1.491067893724177</v>
+        <v>1.516273192042098</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.314831166453966</v>
+        <v>6.171312276307284</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.105743114233346</v>
+        <v>0.1061340607110532</v>
       </c>
       <c r="C46">
-        <v>2917.254091286904</v>
+        <v>2835.392193474594</v>
       </c>
       <c r="D46">
-        <v>4911.170091286904</v>
+        <v>4879.347193474594</v>
       </c>
       <c r="E46">
-        <v>1962.916</v>
+        <v>2012.955</v>
       </c>
       <c r="F46">
-        <v>2201.716</v>
+        <v>2251.755</v>
       </c>
       <c r="G46">
         <v>207.8</v>
@@ -5187,45 +5187,45 @@
         <v>737.8</v>
       </c>
       <c r="M46">
-        <v>119.5531788</v>
+        <v>124.5220515</v>
       </c>
       <c r="N46">
-        <v>618.2468211999999</v>
+        <v>613.2779485</v>
       </c>
       <c r="O46">
-        <v>55.64221390799999</v>
+        <v>55.195015365</v>
       </c>
       <c r="P46">
-        <v>562.6046072919999</v>
+        <v>558.082933135</v>
       </c>
       <c r="Q46">
-        <v>689.4046072919999</v>
+        <v>684.882933135</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1500024897024035</v>
+        <v>0.1517976558382785</v>
       </c>
       <c r="T46">
-        <v>1.516273192042098</v>
+        <v>1.54239504666249</v>
       </c>
       <c r="U46">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.09</v>
       </c>
       <c r="W46">
-        <v>0.04941300000000001</v>
+        <v>0.05032300000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>6.171312276307284</v>
+        <v>5.925054969079111</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1061340607110532</v>
+        <v>0.1061246071887604</v>
       </c>
       <c r="C47">
-        <v>2835.392193474594</v>
+        <v>2786.11784026829</v>
       </c>
       <c r="D47">
-        <v>4879.347193474594</v>
+        <v>4880.111840268291</v>
       </c>
       <c r="E47">
-        <v>2012.955</v>
+        <v>2062.994</v>
       </c>
       <c r="F47">
-        <v>2251.755</v>
+        <v>2301.794</v>
       </c>
       <c r="G47">
         <v>207.8</v>
@@ -5269,28 +5269,28 @@
         <v>737.8</v>
       </c>
       <c r="M47">
-        <v>124.5220515</v>
+        <v>127.2892082</v>
       </c>
       <c r="N47">
-        <v>613.2779485</v>
+        <v>610.5107917999999</v>
       </c>
       <c r="O47">
-        <v>55.195015365</v>
+        <v>54.94597126199999</v>
       </c>
       <c r="P47">
-        <v>558.082933135</v>
+        <v>555.5648205379999</v>
       </c>
       <c r="Q47">
-        <v>684.882933135</v>
+        <v>682.364820538</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1517976558382785</v>
+        <v>0.1536593096088155</v>
       </c>
       <c r="T47">
-        <v>1.54239504666249</v>
+        <v>1.569484377379933</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.925054969079111</v>
+        <v>5.796249426273042</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1061246071887604</v>
+        <v>0.1061151536664676</v>
       </c>
       <c r="C48">
-        <v>2786.11784026829</v>
+        <v>2736.843726756492</v>
       </c>
       <c r="D48">
-        <v>4880.111840268291</v>
+        <v>4880.876726756493</v>
       </c>
       <c r="E48">
-        <v>2062.994</v>
+        <v>2113.033</v>
       </c>
       <c r="F48">
-        <v>2301.794</v>
+        <v>2351.833000000001</v>
       </c>
       <c r="G48">
         <v>207.8</v>
@@ -5351,28 +5351,28 @@
         <v>737.8</v>
       </c>
       <c r="M48">
-        <v>127.2892082</v>
+        <v>130.0563649</v>
       </c>
       <c r="N48">
-        <v>610.5107917999999</v>
+        <v>607.7436350999999</v>
       </c>
       <c r="O48">
-        <v>54.94597126199999</v>
+        <v>54.69692715899999</v>
       </c>
       <c r="P48">
-        <v>555.5648205379999</v>
+        <v>553.0467079409999</v>
       </c>
       <c r="Q48">
-        <v>682.364820538</v>
+        <v>679.846707941</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1536593096088155</v>
+        <v>0.1555912144650332</v>
       </c>
       <c r="T48">
-        <v>1.569484377379933</v>
+        <v>1.597595946992374</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.796249426273042</v>
+        <v>5.672924970394892</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1061151536664676</v>
+        <v>0.1061057001441748</v>
       </c>
       <c r="C49">
-        <v>2736.843726756492</v>
+        <v>2687.569853051926</v>
       </c>
       <c r="D49">
-        <v>4880.876726756493</v>
+        <v>4881.641853051926</v>
       </c>
       <c r="E49">
-        <v>2113.033</v>
+        <v>2163.072</v>
       </c>
       <c r="F49">
-        <v>2351.833000000001</v>
+        <v>2401.872</v>
       </c>
       <c r="G49">
         <v>207.8</v>
@@ -5433,28 +5433,28 @@
         <v>737.8</v>
       </c>
       <c r="M49">
-        <v>130.0563649</v>
+        <v>132.8235216</v>
       </c>
       <c r="N49">
-        <v>607.7436350999999</v>
+        <v>604.9764783999999</v>
       </c>
       <c r="O49">
-        <v>54.69692715899999</v>
+        <v>54.44788305599999</v>
       </c>
       <c r="P49">
-        <v>553.0467079409999</v>
+        <v>550.5285953439999</v>
       </c>
       <c r="Q49">
-        <v>679.846707941</v>
+        <v>677.328595344</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1555912144650332</v>
+        <v>0.1575974233541822</v>
       </c>
       <c r="T49">
-        <v>1.597595946992374</v>
+        <v>1.626788730820677</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.672924970394892</v>
+        <v>5.554739033511665</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1061057001441748</v>
+        <v>0.106096246621882</v>
       </c>
       <c r="C50">
-        <v>2687.569853051926</v>
+        <v>2638.296219267384</v>
       </c>
       <c r="D50">
-        <v>4881.641853051926</v>
+        <v>4882.407219267384</v>
       </c>
       <c r="E50">
-        <v>2163.072</v>
+        <v>2213.111</v>
       </c>
       <c r="F50">
-        <v>2401.872</v>
+        <v>2451.911</v>
       </c>
       <c r="G50">
         <v>207.8</v>
@@ -5515,28 +5515,28 @@
         <v>737.8</v>
       </c>
       <c r="M50">
-        <v>132.8235216</v>
+        <v>135.5906783</v>
       </c>
       <c r="N50">
-        <v>604.9764783999999</v>
+        <v>602.2093216999999</v>
       </c>
       <c r="O50">
-        <v>54.44788305599999</v>
+        <v>54.19883895299999</v>
       </c>
       <c r="P50">
-        <v>550.5285953439999</v>
+        <v>548.010482747</v>
       </c>
       <c r="Q50">
-        <v>677.328595344</v>
+        <v>674.810482747</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1575974233541822</v>
+        <v>0.1596823071017293</v>
       </c>
       <c r="T50">
-        <v>1.626788730820677</v>
+        <v>1.657126329701071</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.554739033511665</v>
+        <v>5.441377012419591</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.106096246621882</v>
+        <v>0.1060867930995892</v>
       </c>
       <c r="C51">
-        <v>2638.296219267384</v>
+        <v>2589.022825515732</v>
       </c>
       <c r="D51">
-        <v>4882.407219267384</v>
+        <v>4883.172825515732</v>
       </c>
       <c r="E51">
-        <v>2213.111</v>
+        <v>2263.15</v>
       </c>
       <c r="F51">
-        <v>2451.911</v>
+        <v>2501.95</v>
       </c>
       <c r="G51">
         <v>207.8</v>
@@ -5597,28 +5597,28 @@
         <v>737.8</v>
       </c>
       <c r="M51">
-        <v>135.5906783</v>
+        <v>138.357835</v>
       </c>
       <c r="N51">
-        <v>602.2093216999999</v>
+        <v>599.4421649999999</v>
       </c>
       <c r="O51">
-        <v>54.19883895299999</v>
+        <v>53.94979484999999</v>
       </c>
       <c r="P51">
-        <v>548.010482747</v>
+        <v>545.4923701499999</v>
       </c>
       <c r="Q51">
-        <v>674.810482747</v>
+        <v>672.29237015</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1596823071017293</v>
+        <v>0.1618505861991783</v>
       </c>
       <c r="T51">
-        <v>1.657126329701071</v>
+        <v>1.688677432536681</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.441377012419591</v>
+        <v>5.332549472171199</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1060867930995892</v>
+        <v>0.1060773395772963</v>
       </c>
       <c r="C52">
-        <v>2589.022825515732</v>
+        <v>2539.749671909906</v>
       </c>
       <c r="D52">
-        <v>4883.172825515732</v>
+        <v>4883.938671909907</v>
       </c>
       <c r="E52">
-        <v>2263.15</v>
+        <v>2313.189</v>
       </c>
       <c r="F52">
-        <v>2501.95</v>
+        <v>2551.989</v>
       </c>
       <c r="G52">
         <v>207.8</v>
@@ -5679,28 +5679,28 @@
         <v>737.8</v>
       </c>
       <c r="M52">
-        <v>138.357835</v>
+        <v>141.1249917</v>
       </c>
       <c r="N52">
-        <v>599.4421649999999</v>
+        <v>596.6750082999999</v>
       </c>
       <c r="O52">
-        <v>53.94979484999999</v>
+        <v>53.70075074699999</v>
       </c>
       <c r="P52">
-        <v>545.4923701499999</v>
+        <v>542.9742575529999</v>
       </c>
       <c r="Q52">
-        <v>672.29237015</v>
+        <v>669.774257553</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1618505861991783</v>
+        <v>0.1641073664842782</v>
       </c>
       <c r="T52">
-        <v>1.688677432536681</v>
+        <v>1.72151633548803</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.332549472171199</v>
+        <v>5.227989678599214</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1060773395772963</v>
+        <v>0.1060678860550035</v>
       </c>
       <c r="C53">
-        <v>2539.749671909906</v>
+        <v>2490.476758562912</v>
       </c>
       <c r="D53">
-        <v>4883.938671909907</v>
+        <v>4884.704758562913</v>
       </c>
       <c r="E53">
-        <v>2313.189</v>
+        <v>2363.228</v>
       </c>
       <c r="F53">
-        <v>2551.989</v>
+        <v>2602.028</v>
       </c>
       <c r="G53">
         <v>207.8</v>
@@ -5761,28 +5761,28 @@
         <v>737.8</v>
       </c>
       <c r="M53">
-        <v>141.1249917</v>
+        <v>143.8921484</v>
       </c>
       <c r="N53">
-        <v>596.6750082999999</v>
+        <v>593.9078516</v>
       </c>
       <c r="O53">
-        <v>53.70075074699999</v>
+        <v>53.45170664399999</v>
       </c>
       <c r="P53">
-        <v>542.9742575529999</v>
+        <v>540.456144956</v>
       </c>
       <c r="Q53">
-        <v>669.774257553</v>
+        <v>667.2561449560001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1641073664842782</v>
+        <v>0.1664581792812574</v>
       </c>
       <c r="T53">
-        <v>1.72151633548803</v>
+        <v>1.755723526062352</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.227989678599214</v>
+        <v>5.127451415549229</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1060678860550035</v>
+        <v>0.1060584325327107</v>
       </c>
       <c r="C54">
-        <v>2490.476758562912</v>
+        <v>2441.204085587828</v>
       </c>
       <c r="D54">
-        <v>4884.704758562913</v>
+        <v>4885.471085587828</v>
       </c>
       <c r="E54">
-        <v>2363.228</v>
+        <v>2413.267</v>
       </c>
       <c r="F54">
-        <v>2602.028</v>
+        <v>2652.067</v>
       </c>
       <c r="G54">
         <v>207.8</v>
@@ -5843,28 +5843,28 @@
         <v>737.8</v>
       </c>
       <c r="M54">
-        <v>143.8921484</v>
+        <v>146.6593051</v>
       </c>
       <c r="N54">
-        <v>593.9078516</v>
+        <v>591.1406949</v>
       </c>
       <c r="O54">
-        <v>53.45170664399999</v>
+        <v>53.202662541</v>
       </c>
       <c r="P54">
-        <v>540.456144956</v>
+        <v>537.938032359</v>
       </c>
       <c r="Q54">
-        <v>667.2561449560001</v>
+        <v>664.738032359</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1664581792812574</v>
+        <v>0.168909026665342</v>
       </c>
       <c r="T54">
-        <v>1.755723526062352</v>
+        <v>1.791386341767496</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.127451415549229</v>
+        <v>5.030707049218112</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1060584325327107</v>
+        <v>0.1060489790104179</v>
       </c>
       <c r="C55">
-        <v>2441.204085587828</v>
+        <v>2391.931653097801</v>
       </c>
       <c r="D55">
-        <v>4885.471085587828</v>
+        <v>4886.237653097802</v>
       </c>
       <c r="E55">
-        <v>2413.267</v>
+        <v>2463.306</v>
       </c>
       <c r="F55">
-        <v>2652.067</v>
+        <v>2702.106000000001</v>
       </c>
       <c r="G55">
         <v>207.8</v>
@@ -5925,28 +5925,28 @@
         <v>737.8</v>
       </c>
       <c r="M55">
-        <v>146.6593051</v>
+        <v>149.4264618000001</v>
       </c>
       <c r="N55">
-        <v>591.1406949</v>
+        <v>588.3735381999999</v>
       </c>
       <c r="O55">
-        <v>53.202662541</v>
+        <v>52.95361843799999</v>
       </c>
       <c r="P55">
-        <v>537.938032359</v>
+        <v>535.4199197619998</v>
       </c>
       <c r="Q55">
-        <v>664.738032359</v>
+        <v>662.2199197619999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.168909026665342</v>
+        <v>0.1714664326313433</v>
       </c>
       <c r="T55">
-        <v>1.791386341767496</v>
+        <v>1.828599714677212</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.030707049218112</v>
+        <v>4.937545807565924</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1060489790104179</v>
+        <v>0.1060395254881251</v>
       </c>
       <c r="C56">
-        <v>2391.931653097801</v>
+        <v>2342.659461206052</v>
       </c>
       <c r="D56">
-        <v>4886.237653097802</v>
+        <v>4887.004461206052</v>
       </c>
       <c r="E56">
-        <v>2463.306</v>
+        <v>2513.345</v>
       </c>
       <c r="F56">
-        <v>2702.106000000001</v>
+        <v>2752.145</v>
       </c>
       <c r="G56">
         <v>207.8</v>
@@ -6007,28 +6007,28 @@
         <v>737.8</v>
       </c>
       <c r="M56">
-        <v>149.4264618000001</v>
+        <v>152.1936185</v>
       </c>
       <c r="N56">
-        <v>588.3735381999999</v>
+        <v>585.6063814999999</v>
       </c>
       <c r="O56">
-        <v>52.95361843799999</v>
+        <v>52.70457433499999</v>
       </c>
       <c r="P56">
-        <v>535.4199197619998</v>
+        <v>532.9018071649999</v>
       </c>
       <c r="Q56">
-        <v>662.2199197619999</v>
+        <v>659.701807165</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1714664326313433</v>
+        <v>0.1741375010847225</v>
       </c>
       <c r="T56">
-        <v>1.828599714677212</v>
+        <v>1.867467015271804</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.937545807565924</v>
+        <v>4.847772247428361</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1060395254881251</v>
+        <v>0.1060300719658323</v>
       </c>
       <c r="C57">
-        <v>2342.659461206052</v>
+        <v>2293.387510025872</v>
       </c>
       <c r="D57">
-        <v>4887.004461206052</v>
+        <v>4887.771510025873</v>
       </c>
       <c r="E57">
-        <v>2513.345</v>
+        <v>2563.384</v>
       </c>
       <c r="F57">
-        <v>2752.145</v>
+        <v>2802.184000000001</v>
       </c>
       <c r="G57">
         <v>207.8</v>
@@ -6089,28 +6089,28 @@
         <v>737.8</v>
       </c>
       <c r="M57">
-        <v>152.1936185</v>
+        <v>154.9607752</v>
       </c>
       <c r="N57">
-        <v>585.6063814999999</v>
+        <v>582.8392247999999</v>
       </c>
       <c r="O57">
-        <v>52.70457433499999</v>
+        <v>52.45553023199999</v>
       </c>
       <c r="P57">
-        <v>532.9018071649999</v>
+        <v>530.3836945679999</v>
       </c>
       <c r="Q57">
-        <v>659.701807165</v>
+        <v>657.183694568</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1741375010847225</v>
+        <v>0.176929981740528</v>
       </c>
       <c r="T57">
-        <v>1.867467015271804</v>
+        <v>1.908101011347968</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.847772247428361</v>
+        <v>4.761204885867142</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1060300719658323</v>
+        <v>0.1060206184435395</v>
       </c>
       <c r="C58">
-        <v>2293.387510025872</v>
+        <v>2244.115799670623</v>
       </c>
       <c r="D58">
-        <v>4887.771510025873</v>
+        <v>4888.538799670623</v>
       </c>
       <c r="E58">
-        <v>2563.384</v>
+        <v>2613.423</v>
       </c>
       <c r="F58">
-        <v>2802.184000000001</v>
+        <v>2852.223</v>
       </c>
       <c r="G58">
         <v>207.8</v>
@@ -6171,28 +6171,28 @@
         <v>737.8</v>
       </c>
       <c r="M58">
-        <v>154.9607752</v>
+        <v>157.7279319</v>
       </c>
       <c r="N58">
-        <v>582.8392247999999</v>
+        <v>580.0720680999999</v>
       </c>
       <c r="O58">
-        <v>52.45553023199999</v>
+        <v>52.20648612899999</v>
       </c>
       <c r="P58">
-        <v>530.3836945679999</v>
+        <v>527.8655819709999</v>
       </c>
       <c r="Q58">
-        <v>657.183694568</v>
+        <v>654.6655819709999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.176929981740528</v>
+        <v>0.1798523452175337</v>
       </c>
       <c r="T58">
-        <v>1.908101011347968</v>
+        <v>1.950624960730001</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.761204885867142</v>
+        <v>4.677674975588771</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1060206184435395</v>
+        <v>0.1060111649212467</v>
       </c>
       <c r="C59">
-        <v>2244.115799670623</v>
+        <v>2194.844330253734</v>
       </c>
       <c r="D59">
-        <v>4888.538799670623</v>
+        <v>4889.306330253735</v>
       </c>
       <c r="E59">
-        <v>2613.423</v>
+        <v>2663.462</v>
       </c>
       <c r="F59">
-        <v>2852.223</v>
+        <v>2902.262000000001</v>
       </c>
       <c r="G59">
         <v>207.8</v>
@@ -6253,28 +6253,28 @@
         <v>737.8</v>
       </c>
       <c r="M59">
-        <v>157.7279319</v>
+        <v>160.4950886</v>
       </c>
       <c r="N59">
-        <v>580.0720680999999</v>
+        <v>577.3049113999999</v>
       </c>
       <c r="O59">
-        <v>52.20648612899999</v>
+        <v>51.95744202599999</v>
       </c>
       <c r="P59">
-        <v>527.8655819709999</v>
+        <v>525.347469374</v>
       </c>
       <c r="Q59">
-        <v>654.6655819709999</v>
+        <v>652.147469374</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1798523452175337</v>
+        <v>0.1829138688601112</v>
       </c>
       <c r="T59">
-        <v>1.950624960730001</v>
+        <v>1.995173860082606</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.677674975588771</v>
+        <v>4.597025407044137</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1060111649212467</v>
+        <v>0.1060017113989539</v>
       </c>
       <c r="C60">
-        <v>2194.844330253734</v>
+        <v>2145.573101888715</v>
       </c>
       <c r="D60">
-        <v>4889.306330253734</v>
+        <v>4890.074101888716</v>
       </c>
       <c r="E60">
-        <v>2663.462</v>
+        <v>2713.501</v>
       </c>
       <c r="F60">
-        <v>2902.262</v>
+        <v>2952.301</v>
       </c>
       <c r="G60">
         <v>207.8</v>
@@ -6335,28 +6335,28 @@
         <v>737.8</v>
       </c>
       <c r="M60">
-        <v>160.4950886</v>
+        <v>163.2622453</v>
       </c>
       <c r="N60">
-        <v>577.3049113999999</v>
+        <v>574.5377546999999</v>
       </c>
       <c r="O60">
-        <v>51.95744202599999</v>
+        <v>51.70839792299999</v>
       </c>
       <c r="P60">
-        <v>525.347469374</v>
+        <v>522.8293567769999</v>
       </c>
       <c r="Q60">
-        <v>652.147469374</v>
+        <v>649.629356777</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1829138688601112</v>
+        <v>0.1861247351193997</v>
       </c>
       <c r="T60">
-        <v>1.995173860082606</v>
+        <v>2.041895876476802</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.597025407044137</v>
+        <v>4.519109722178982</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1060017113989539</v>
+        <v>0.1073572578766611</v>
       </c>
       <c r="C61">
-        <v>2145.573101888715</v>
+        <v>1987.850248624426</v>
       </c>
       <c r="D61">
-        <v>4890.074101888716</v>
+        <v>4782.390248624426</v>
       </c>
       <c r="E61">
-        <v>2713.501</v>
+        <v>2763.54</v>
       </c>
       <c r="F61">
-        <v>2952.301</v>
+        <v>3002.34</v>
       </c>
       <c r="G61">
         <v>207.8</v>
@@ -6417,45 +6417,45 @@
         <v>737.8</v>
       </c>
       <c r="M61">
-        <v>163.2622453</v>
+        <v>173.535252</v>
       </c>
       <c r="N61">
-        <v>574.5377546999999</v>
+        <v>564.2647479999999</v>
       </c>
       <c r="O61">
-        <v>51.70839792299999</v>
+        <v>50.78382731999999</v>
       </c>
       <c r="P61">
-        <v>522.8293567769999</v>
+        <v>513.4809206799999</v>
       </c>
       <c r="Q61">
-        <v>649.629356777</v>
+        <v>640.28092068</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1861247351193997</v>
+        <v>0.1894961446916527</v>
       </c>
       <c r="T61">
-        <v>2.041895876476802</v>
+        <v>2.090953993690707</v>
       </c>
       <c r="U61">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V61">
         <v>0.09</v>
       </c>
       <c r="W61">
-        <v>0.05032300000000001</v>
+        <v>0.05259800000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.519109722178982</v>
+        <v>4.251585723919655</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1073572578766611</v>
+        <v>0.1073705543543683</v>
       </c>
       <c r="C62">
-        <v>1987.850248624426</v>
+        <v>1936.778466867062</v>
       </c>
       <c r="D62">
-        <v>4782.390248624426</v>
+        <v>4781.357466867062</v>
       </c>
       <c r="E62">
-        <v>2763.54</v>
+        <v>2813.579</v>
       </c>
       <c r="F62">
-        <v>3002.34</v>
+        <v>3052.379</v>
       </c>
       <c r="G62">
         <v>207.8</v>
@@ -6499,28 +6499,28 @@
         <v>737.8</v>
       </c>
       <c r="M62">
-        <v>173.535252</v>
+        <v>176.4275062</v>
       </c>
       <c r="N62">
-        <v>564.2647479999999</v>
+        <v>561.3724937999999</v>
       </c>
       <c r="O62">
-        <v>50.78382731999999</v>
+        <v>50.52352444199999</v>
       </c>
       <c r="P62">
-        <v>513.4809206799999</v>
+        <v>510.8489693579999</v>
       </c>
       <c r="Q62">
-        <v>640.28092068</v>
+        <v>637.6489693579999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1894961446916527</v>
+        <v>0.1930404470624828</v>
       </c>
       <c r="T62">
-        <v>2.090953993690707</v>
+        <v>2.142527911787377</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.251585723919655</v>
+        <v>4.181887597298021</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1073705543543683</v>
+        <v>0.1073838508320755</v>
       </c>
       <c r="C63">
-        <v>1936.778466867062</v>
+        <v>1885.707131082449</v>
       </c>
       <c r="D63">
-        <v>4781.357466867062</v>
+        <v>4780.325131082449</v>
       </c>
       <c r="E63">
-        <v>2813.579</v>
+        <v>2863.618</v>
       </c>
       <c r="F63">
-        <v>3052.379</v>
+        <v>3102.418</v>
       </c>
       <c r="G63">
         <v>207.8</v>
@@ -6581,28 +6581,28 @@
         <v>737.8</v>
       </c>
       <c r="M63">
-        <v>176.4275062</v>
+        <v>179.3197604</v>
       </c>
       <c r="N63">
-        <v>561.3724937999999</v>
+        <v>558.4802396</v>
       </c>
       <c r="O63">
-        <v>50.52352444199999</v>
+        <v>50.263221564</v>
       </c>
       <c r="P63">
-        <v>510.8489693579999</v>
+        <v>508.217018036</v>
       </c>
       <c r="Q63">
-        <v>637.6489693579999</v>
+        <v>635.0170180360001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1930404470624828</v>
+        <v>0.1967712916633565</v>
       </c>
       <c r="T63">
-        <v>2.142527911787377</v>
+        <v>2.196816246625978</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.181887597298021</v>
+        <v>4.114437797341603</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1073838508320755</v>
+        <v>0.1073971473097827</v>
       </c>
       <c r="C64">
-        <v>1885.707131082449</v>
+        <v>1834.636240981777</v>
       </c>
       <c r="D64">
-        <v>4780.325131082449</v>
+        <v>4779.293240981777</v>
       </c>
       <c r="E64">
-        <v>2863.618</v>
+        <v>2913.657</v>
       </c>
       <c r="F64">
-        <v>3102.418</v>
+        <v>3152.457</v>
       </c>
       <c r="G64">
         <v>207.8</v>
@@ -6663,28 +6663,28 @@
         <v>737.8</v>
       </c>
       <c r="M64">
-        <v>179.3197604</v>
+        <v>182.2120146</v>
       </c>
       <c r="N64">
-        <v>558.4802396</v>
+        <v>555.5879854</v>
       </c>
       <c r="O64">
-        <v>50.263221564</v>
+        <v>50.00291868599999</v>
       </c>
       <c r="P64">
-        <v>508.217018036</v>
+        <v>505.585066714</v>
       </c>
       <c r="Q64">
-        <v>635.0170180360001</v>
+        <v>632.385066714</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1967712916633565</v>
+        <v>0.2007038035399532</v>
       </c>
       <c r="T64">
-        <v>2.196816246625978</v>
+        <v>2.254039086050448</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.114437797341603</v>
+        <v>4.049129260875862</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1073971473097827</v>
+        <v>0.1094488437874899</v>
       </c>
       <c r="C65">
-        <v>1834.636240981777</v>
+        <v>1630.538525615459</v>
       </c>
       <c r="D65">
-        <v>4779.293240981777</v>
+        <v>4625.234525615459</v>
       </c>
       <c r="E65">
-        <v>2913.657</v>
+        <v>2963.696</v>
       </c>
       <c r="F65">
-        <v>3152.457</v>
+        <v>3202.496000000001</v>
       </c>
       <c r="G65">
         <v>207.8</v>
@@ -6745,45 +6745,45 @@
         <v>737.8</v>
       </c>
       <c r="M65">
-        <v>182.2120146</v>
+        <v>196.3130048</v>
       </c>
       <c r="N65">
-        <v>555.5879854</v>
+        <v>541.4869951999999</v>
       </c>
       <c r="O65">
-        <v>50.00291868599999</v>
+        <v>48.73382956799999</v>
       </c>
       <c r="P65">
-        <v>505.585066714</v>
+        <v>492.7531656319999</v>
       </c>
       <c r="Q65">
-        <v>632.385066714</v>
+        <v>619.5531656319999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2007038035399532</v>
+        <v>0.2048547882985829</v>
       </c>
       <c r="T65">
-        <v>2.254039086050448</v>
+        <v>2.314440972109611</v>
       </c>
       <c r="U65">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V65">
         <v>0.09</v>
       </c>
       <c r="W65">
-        <v>0.05259800000000001</v>
+        <v>0.055783</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>4.049129260875862</v>
+        <v>3.75828387299994</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1094488437874899</v>
+        <v>0.109493990265197</v>
       </c>
       <c r="C66">
-        <v>1630.538525615459</v>
+        <v>1577.221146501012</v>
       </c>
       <c r="D66">
-        <v>4625.234525615459</v>
+        <v>4621.956146501012</v>
       </c>
       <c r="E66">
-        <v>2963.696</v>
+        <v>3013.735</v>
       </c>
       <c r="F66">
-        <v>3202.496000000001</v>
+        <v>3252.535</v>
       </c>
       <c r="G66">
         <v>207.8</v>
@@ -6827,28 +6827,28 @@
         <v>737.8</v>
       </c>
       <c r="M66">
-        <v>196.3130048</v>
+        <v>199.3803955</v>
       </c>
       <c r="N66">
-        <v>541.4869951999999</v>
+        <v>538.4196044999999</v>
       </c>
       <c r="O66">
-        <v>48.73382956799999</v>
+        <v>48.45776440499998</v>
       </c>
       <c r="P66">
-        <v>492.7531656319999</v>
+        <v>489.9618400949999</v>
       </c>
       <c r="Q66">
-        <v>619.5531656319999</v>
+        <v>616.761840095</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2048547882985829</v>
+        <v>0.2092429721862773</v>
       </c>
       <c r="T66">
-        <v>2.314440972109611</v>
+        <v>2.378294394515012</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.75828387299994</v>
+        <v>3.700464121107633</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.109493990265197</v>
+        <v>0.1095391367429042</v>
       </c>
       <c r="C67">
-        <v>1577.221146501012</v>
+        <v>1523.908411543268</v>
       </c>
       <c r="D67">
-        <v>4621.956146501012</v>
+        <v>4618.682411543268</v>
       </c>
       <c r="E67">
-        <v>3013.735</v>
+        <v>3063.774</v>
       </c>
       <c r="F67">
-        <v>3252.535</v>
+        <v>3302.574000000001</v>
       </c>
       <c r="G67">
         <v>207.8</v>
@@ -6909,28 +6909,28 @@
         <v>737.8</v>
       </c>
       <c r="M67">
-        <v>199.3803955</v>
+        <v>202.4477862</v>
       </c>
       <c r="N67">
-        <v>538.4196044999999</v>
+        <v>535.3522138</v>
       </c>
       <c r="O67">
-        <v>48.45776440499998</v>
+        <v>48.18169924199999</v>
       </c>
       <c r="P67">
-        <v>489.9618400949999</v>
+        <v>487.170514558</v>
       </c>
       <c r="Q67">
-        <v>616.761840095</v>
+        <v>613.9705145580001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2092429721862773</v>
+        <v>0.2138892845379537</v>
       </c>
       <c r="T67">
-        <v>2.378294394515012</v>
+        <v>2.445903900591319</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.700464121107633</v>
+        <v>3.644396482909033</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1095391367429042</v>
+        <v>0.1095842832206115</v>
       </c>
       <c r="C68">
-        <v>1523.908411543268</v>
+        <v>1470.600310880834</v>
       </c>
       <c r="D68">
-        <v>4618.682411543268</v>
+        <v>4615.413310880835</v>
       </c>
       <c r="E68">
-        <v>3063.774</v>
+        <v>3113.813000000001</v>
       </c>
       <c r="F68">
-        <v>3302.574000000001</v>
+        <v>3352.613000000001</v>
       </c>
       <c r="G68">
         <v>207.8</v>
@@ -6991,28 +6991,28 @@
         <v>737.8</v>
       </c>
       <c r="M68">
-        <v>202.4477862</v>
+        <v>205.5151769000001</v>
       </c>
       <c r="N68">
-        <v>535.3522138</v>
+        <v>532.2848230999999</v>
       </c>
       <c r="O68">
-        <v>48.18169924199999</v>
+        <v>47.905634079</v>
       </c>
       <c r="P68">
-        <v>487.170514558</v>
+        <v>484.3791890209999</v>
       </c>
       <c r="Q68">
-        <v>613.9705145580001</v>
+        <v>611.179189021</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2138892845379537</v>
+        <v>0.2188171915776105</v>
       </c>
       <c r="T68">
-        <v>2.445903900591319</v>
+        <v>2.517610952490433</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.644396482909033</v>
+        <v>3.590002505552181</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1095842832206115</v>
+        <v>0.1096294296983187</v>
       </c>
       <c r="C69">
-        <v>1470.600310880834</v>
+        <v>1417.296834680215</v>
       </c>
       <c r="D69">
-        <v>4615.413310880835</v>
+        <v>4612.148834680215</v>
       </c>
       <c r="E69">
-        <v>3113.813000000001</v>
+        <v>3163.852</v>
       </c>
       <c r="F69">
-        <v>3352.613000000001</v>
+        <v>3402.652</v>
       </c>
       <c r="G69">
         <v>207.8</v>
@@ -7073,28 +7073,28 @@
         <v>737.8</v>
       </c>
       <c r="M69">
-        <v>205.5151769000001</v>
+        <v>208.5825676</v>
       </c>
       <c r="N69">
-        <v>532.2848230999999</v>
+        <v>529.2174323999999</v>
       </c>
       <c r="O69">
-        <v>47.905634079</v>
+        <v>47.62956891599999</v>
       </c>
       <c r="P69">
-        <v>484.3791890209999</v>
+        <v>481.5878634839999</v>
       </c>
       <c r="Q69">
-        <v>611.179189021</v>
+        <v>608.387863484</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2188171915776105</v>
+        <v>0.2240530928072458</v>
       </c>
       <c r="T69">
-        <v>2.517610952490433</v>
+        <v>2.593799695133241</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.590002505552181</v>
+        <v>3.537208351058767</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1096294296983187</v>
+        <v>0.1114326961760258</v>
       </c>
       <c r="C70">
-        <v>1417.296834680215</v>
+        <v>1240.538472710547</v>
       </c>
       <c r="D70">
-        <v>4612.148834680215</v>
+        <v>4485.429472710548</v>
       </c>
       <c r="E70">
-        <v>3163.852</v>
+        <v>3213.891000000001</v>
       </c>
       <c r="F70">
-        <v>3402.652</v>
+        <v>3452.691000000001</v>
       </c>
       <c r="G70">
         <v>207.8</v>
@@ -7155,45 +7155,45 @@
         <v>737.8</v>
       </c>
       <c r="M70">
-        <v>208.5825676</v>
+        <v>221.3174931000001</v>
       </c>
       <c r="N70">
-        <v>529.2174323999999</v>
+        <v>516.4825068999999</v>
       </c>
       <c r="O70">
-        <v>47.62956891599999</v>
+        <v>46.48342562099999</v>
       </c>
       <c r="P70">
-        <v>481.5878634839999</v>
+        <v>469.9990812789999</v>
       </c>
       <c r="Q70">
-        <v>608.387863484</v>
+        <v>596.7990812789999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2240530928072458</v>
+        <v>0.2296267941162124</v>
       </c>
       <c r="T70">
-        <v>2.593799695133241</v>
+        <v>2.674903840527198</v>
       </c>
       <c r="U70">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V70">
         <v>0.09</v>
       </c>
       <c r="W70">
-        <v>0.055783</v>
+        <v>0.05833100000000001</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>3.537208351058767</v>
+        <v>3.333672316930829</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1114326961760258</v>
+        <v>0.111503322653733</v>
       </c>
       <c r="C71">
-        <v>1240.538472710547</v>
+        <v>1185.677949660166</v>
       </c>
       <c r="D71">
-        <v>4485.429472710548</v>
+        <v>4480.607949660167</v>
       </c>
       <c r="E71">
-        <v>3213.891000000001</v>
+        <v>3263.930000000001</v>
       </c>
       <c r="F71">
-        <v>3452.691000000001</v>
+        <v>3502.730000000001</v>
       </c>
       <c r="G71">
         <v>207.8</v>
@@ -7237,28 +7237,28 @@
         <v>737.8</v>
       </c>
       <c r="M71">
-        <v>221.3174931000001</v>
+        <v>224.5249930000001</v>
       </c>
       <c r="N71">
-        <v>516.4825068999999</v>
+        <v>513.2750069999998</v>
       </c>
       <c r="O71">
-        <v>46.48342562099999</v>
+        <v>46.19475062999999</v>
       </c>
       <c r="P71">
-        <v>469.9990812789999</v>
+        <v>467.0802563699999</v>
       </c>
       <c r="Q71">
-        <v>596.7990812789999</v>
+        <v>593.8802563699999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2296267941162124</v>
+        <v>0.2355720755124434</v>
       </c>
       <c r="T71">
-        <v>2.674903840527198</v>
+        <v>2.761414928947418</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.333672316930829</v>
+        <v>3.28604842668896</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.111503322653733</v>
+        <v>0.1115739491314402</v>
       </c>
       <c r="C72">
-        <v>1185.677949660166</v>
+        <v>1130.827781079746</v>
       </c>
       <c r="D72">
-        <v>4480.607949660167</v>
+        <v>4475.796781079746</v>
       </c>
       <c r="E72">
-        <v>3263.930000000001</v>
+        <v>3313.969000000001</v>
       </c>
       <c r="F72">
-        <v>3502.730000000001</v>
+        <v>3552.769000000001</v>
       </c>
       <c r="G72">
         <v>207.8</v>
@@ -7319,28 +7319,28 @@
         <v>737.8</v>
       </c>
       <c r="M72">
-        <v>224.5249930000001</v>
+        <v>227.7324929000001</v>
       </c>
       <c r="N72">
-        <v>513.2750069999998</v>
+        <v>510.0675070999999</v>
       </c>
       <c r="O72">
-        <v>46.19475062999999</v>
+        <v>45.90607563899999</v>
       </c>
       <c r="P72">
-        <v>467.0802563699999</v>
+        <v>464.1614314609999</v>
       </c>
       <c r="Q72">
-        <v>593.8802563699999</v>
+        <v>590.961431461</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2355720755124434</v>
+        <v>0.2419273763153111</v>
       </c>
       <c r="T72">
-        <v>2.761414928947418</v>
+        <v>2.853892299327654</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.28604842668896</v>
+        <v>3.239766054482073</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1115739491314402</v>
+        <v>0.1116445756091474</v>
       </c>
       <c r="C73">
-        <v>1130.827781079747</v>
+        <v>1075.987933649925</v>
       </c>
       <c r="D73">
-        <v>4475.796781079747</v>
+        <v>4470.995933649925</v>
       </c>
       <c r="E73">
-        <v>3313.969</v>
+        <v>3364.008</v>
       </c>
       <c r="F73">
-        <v>3552.769</v>
+        <v>3602.808</v>
       </c>
       <c r="G73">
         <v>207.8</v>
@@ -7401,28 +7401,28 @@
         <v>737.8</v>
       </c>
       <c r="M73">
-        <v>227.7324929</v>
+        <v>230.9399928000001</v>
       </c>
       <c r="N73">
-        <v>510.0675070999999</v>
+        <v>506.8600071999999</v>
       </c>
       <c r="O73">
-        <v>45.90607563899999</v>
+        <v>45.61740064799999</v>
       </c>
       <c r="P73">
-        <v>464.1614314609999</v>
+        <v>461.2426065519999</v>
       </c>
       <c r="Q73">
-        <v>590.9614314610001</v>
+        <v>588.0426065520001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2419273763153111</v>
+        <v>0.2487366271755264</v>
       </c>
       <c r="T73">
-        <v>2.853892299327653</v>
+        <v>2.95297519616362</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.239766054482074</v>
+        <v>3.194769303725378</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1116445756091474</v>
+        <v>0.1117152020868546</v>
       </c>
       <c r="C74">
-        <v>1075.987933649925</v>
+        <v>1021.158374194145</v>
       </c>
       <c r="D74">
-        <v>4470.995933649925</v>
+        <v>4466.205374194145</v>
       </c>
       <c r="E74">
-        <v>3364.008</v>
+        <v>3414.047</v>
       </c>
       <c r="F74">
-        <v>3602.808</v>
+        <v>3652.847</v>
       </c>
       <c r="G74">
         <v>207.8</v>
@@ -7483,28 +7483,28 @@
         <v>737.8</v>
       </c>
       <c r="M74">
-        <v>230.9399928000001</v>
+        <v>234.1474927</v>
       </c>
       <c r="N74">
-        <v>506.8600071999999</v>
+        <v>503.6525072999999</v>
       </c>
       <c r="O74">
-        <v>45.61740064799999</v>
+        <v>45.32872565699999</v>
       </c>
       <c r="P74">
-        <v>461.2426065519999</v>
+        <v>458.3237816429999</v>
       </c>
       <c r="Q74">
-        <v>588.0426065520001</v>
+        <v>585.123781643</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2487366271755264</v>
+        <v>0.2560502669883503</v>
       </c>
       <c r="T74">
-        <v>2.95297519616362</v>
+        <v>3.059397566839289</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.194769303725378</v>
+        <v>3.151005340660647</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1117152020868546</v>
+        <v>0.1117858285645618</v>
       </c>
       <c r="C75">
-        <v>1021.158374194145</v>
+        <v>966.3390696778852</v>
       </c>
       <c r="D75">
-        <v>4466.205374194145</v>
+        <v>4461.425069677885</v>
       </c>
       <c r="E75">
-        <v>3414.047</v>
+        <v>3464.086</v>
       </c>
       <c r="F75">
-        <v>3652.847</v>
+        <v>3702.886</v>
       </c>
       <c r="G75">
         <v>207.8</v>
@@ -7565,28 +7565,28 @@
         <v>737.8</v>
       </c>
       <c r="M75">
-        <v>234.1474927</v>
+        <v>237.3549926</v>
       </c>
       <c r="N75">
-        <v>503.6525072999999</v>
+        <v>500.4450073999999</v>
       </c>
       <c r="O75">
-        <v>45.32872565699999</v>
+        <v>45.04005066599999</v>
       </c>
       <c r="P75">
-        <v>458.3237816429999</v>
+        <v>455.4049567339999</v>
       </c>
       <c r="Q75">
-        <v>585.123781643</v>
+        <v>582.204956734</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2560502669883503</v>
+        <v>0.2639264944790838</v>
       </c>
       <c r="T75">
-        <v>3.059397566839289</v>
+        <v>3.174006273720777</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.151005340660647</v>
+        <v>3.108424187408476</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1117858285645618</v>
+        <v>0.111856455042269</v>
       </c>
       <c r="C76">
-        <v>966.3390696778852</v>
+        <v>911.5299872079095</v>
       </c>
       <c r="D76">
-        <v>4461.425069677885</v>
+        <v>4456.654987207909</v>
       </c>
       <c r="E76">
-        <v>3464.086</v>
+        <v>3514.125</v>
       </c>
       <c r="F76">
-        <v>3702.886</v>
+        <v>3752.925</v>
       </c>
       <c r="G76">
         <v>207.8</v>
@@ -7647,28 +7647,28 @@
         <v>737.8</v>
       </c>
       <c r="M76">
-        <v>237.3549926</v>
+        <v>240.5624925</v>
       </c>
       <c r="N76">
-        <v>500.4450073999999</v>
+        <v>497.2375074999999</v>
       </c>
       <c r="O76">
-        <v>45.04005066599999</v>
+        <v>44.75137567499999</v>
       </c>
       <c r="P76">
-        <v>455.4049567339999</v>
+        <v>452.4861318249999</v>
       </c>
       <c r="Q76">
-        <v>582.204956734</v>
+        <v>579.286131825</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2639264944790838</v>
+        <v>0.2724328201690759</v>
       </c>
       <c r="T76">
-        <v>3.174006273720777</v>
+        <v>3.297783677152786</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.108424187408476</v>
+        <v>3.066978531576363</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.111856455042269</v>
+        <v>0.1119270815199762</v>
       </c>
       <c r="C77">
-        <v>911.5299872079095</v>
+        <v>856.7310940315024</v>
       </c>
       <c r="D77">
-        <v>4456.654987207909</v>
+        <v>4451.895094031503</v>
       </c>
       <c r="E77">
-        <v>3514.125</v>
+        <v>3564.164</v>
       </c>
       <c r="F77">
-        <v>3752.925</v>
+        <v>3802.964</v>
       </c>
       <c r="G77">
         <v>207.8</v>
@@ -7729,28 +7729,28 @@
         <v>737.8</v>
       </c>
       <c r="M77">
-        <v>240.5624925</v>
+        <v>243.7699924</v>
       </c>
       <c r="N77">
-        <v>497.2375074999999</v>
+        <v>494.0300075999999</v>
       </c>
       <c r="O77">
-        <v>44.75137567499999</v>
+        <v>44.46270068399999</v>
       </c>
       <c r="P77">
-        <v>452.4861318249999</v>
+        <v>449.5673069159999</v>
       </c>
       <c r="Q77">
-        <v>579.286131825</v>
+        <v>576.367306916</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2724328201690759</v>
+        <v>0.2816480063332341</v>
       </c>
       <c r="T77">
-        <v>3.297783677152786</v>
+        <v>3.431875864204128</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.066978531576363</v>
+        <v>3.026623550897727</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1119270815199762</v>
+        <v>0.1174631679976834</v>
       </c>
       <c r="C78">
-        <v>856.7310940315024</v>
+        <v>462.7765664478547</v>
       </c>
       <c r="D78">
-        <v>4451.895094031503</v>
+        <v>4107.979566447855</v>
       </c>
       <c r="E78">
-        <v>3564.164</v>
+        <v>3614.203</v>
       </c>
       <c r="F78">
-        <v>3802.964</v>
+        <v>3853.003000000001</v>
       </c>
       <c r="G78">
         <v>207.8</v>
@@ -7811,45 +7811,45 @@
         <v>737.8</v>
       </c>
       <c r="M78">
-        <v>243.7699924</v>
+        <v>277.0309157000001</v>
       </c>
       <c r="N78">
-        <v>494.0300075999999</v>
+        <v>460.7690842999999</v>
       </c>
       <c r="O78">
-        <v>44.46270068399999</v>
+        <v>41.46921758699999</v>
       </c>
       <c r="P78">
-        <v>449.5673069159999</v>
+        <v>419.2998667129999</v>
       </c>
       <c r="Q78">
-        <v>576.367306916</v>
+        <v>546.099866713</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2816480063332341</v>
+        <v>0.291664513033406</v>
       </c>
       <c r="T78">
-        <v>3.431875864204128</v>
+        <v>3.577628241433848</v>
       </c>
       <c r="U78">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V78">
         <v>0.09</v>
       </c>
       <c r="W78">
-        <v>0.05833100000000001</v>
+        <v>0.065429</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>3.026623550897727</v>
+        <v>2.663240664442563</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1174631679976834</v>
+        <v>0.1176047744753906</v>
       </c>
       <c r="C79">
-        <v>462.7765664478547</v>
+        <v>404.6362038135758</v>
       </c>
       <c r="D79">
-        <v>4107.979566447855</v>
+        <v>4099.878203813576</v>
       </c>
       <c r="E79">
-        <v>3614.203</v>
+        <v>3664.242</v>
       </c>
       <c r="F79">
-        <v>3853.003000000001</v>
+        <v>3903.042</v>
       </c>
       <c r="G79">
         <v>207.8</v>
@@ -7893,28 +7893,28 @@
         <v>737.8</v>
       </c>
       <c r="M79">
-        <v>277.0309157000001</v>
+        <v>280.6287198000001</v>
       </c>
       <c r="N79">
-        <v>460.7690842999999</v>
+        <v>457.1712801999999</v>
       </c>
       <c r="O79">
-        <v>41.46921758699999</v>
+        <v>41.14541521799999</v>
       </c>
       <c r="P79">
-        <v>419.2998667129999</v>
+        <v>416.0258649819999</v>
       </c>
       <c r="Q79">
-        <v>546.099866713</v>
+        <v>542.825864982</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.291664513033406</v>
+        <v>0.3025916112517753</v>
       </c>
       <c r="T79">
-        <v>3.577628241433848</v>
+        <v>3.73663083477536</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.663240664442563</v>
+        <v>2.629096553359966</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1176047744753906</v>
+        <v>0.1177463809530978</v>
       </c>
       <c r="C80">
-        <v>404.6362038135758</v>
+        <v>346.5277317459099</v>
       </c>
       <c r="D80">
-        <v>4099.878203813576</v>
+        <v>4091.808731745911</v>
       </c>
       <c r="E80">
-        <v>3664.242</v>
+        <v>3714.281</v>
       </c>
       <c r="F80">
-        <v>3903.042</v>
+        <v>3953.081000000001</v>
       </c>
       <c r="G80">
         <v>207.8</v>
@@ -7975,28 +7975,28 @@
         <v>737.8</v>
       </c>
       <c r="M80">
-        <v>280.6287198000001</v>
+        <v>284.2265239000001</v>
       </c>
       <c r="N80">
-        <v>457.1712801999999</v>
+        <v>453.5734760999999</v>
       </c>
       <c r="O80">
-        <v>41.14541521799999</v>
+        <v>40.82161284899999</v>
       </c>
       <c r="P80">
-        <v>416.0258649819999</v>
+        <v>412.7518632509999</v>
       </c>
       <c r="Q80">
-        <v>542.825864982</v>
+        <v>539.551863251</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3025916112517753</v>
+        <v>0.3145593854909418</v>
       </c>
       <c r="T80">
-        <v>3.73663083477536</v>
+        <v>3.910776532244636</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.629096553359966</v>
+        <v>2.595816850152878</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1177463809530978</v>
+        <v>0.117887987430805</v>
       </c>
       <c r="C81">
-        <v>346.5277317459099</v>
+        <v>288.4509623115746</v>
       </c>
       <c r="D81">
-        <v>4091.808731745911</v>
+        <v>4083.770962311575</v>
       </c>
       <c r="E81">
-        <v>3714.281</v>
+        <v>3764.320000000001</v>
       </c>
       <c r="F81">
-        <v>3953.081000000001</v>
+        <v>4003.120000000001</v>
       </c>
       <c r="G81">
         <v>207.8</v>
@@ -8057,28 +8057,28 @@
         <v>737.8</v>
       </c>
       <c r="M81">
-        <v>284.2265239000001</v>
+        <v>287.8243280000001</v>
       </c>
       <c r="N81">
-        <v>453.5734760999999</v>
+        <v>449.9756719999999</v>
       </c>
       <c r="O81">
-        <v>40.82161284899999</v>
+        <v>40.49781047999998</v>
       </c>
       <c r="P81">
-        <v>412.7518632509999</v>
+        <v>409.4778615199999</v>
       </c>
       <c r="Q81">
-        <v>539.551863251</v>
+        <v>536.27786152</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3145593854909418</v>
+        <v>0.3277239371540248</v>
       </c>
       <c r="T81">
-        <v>3.910776532244636</v>
+        <v>4.102336799460839</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.595816850152878</v>
+        <v>2.563369139525967</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.117887987430805</v>
+        <v>0.1180295939085121</v>
       </c>
       <c r="C82">
-        <v>288.4509623115746</v>
+        <v>230.4057090510578</v>
       </c>
       <c r="D82">
-        <v>4083.770962311575</v>
+        <v>4075.764709051059</v>
       </c>
       <c r="E82">
-        <v>3764.320000000001</v>
+        <v>3814.359</v>
       </c>
       <c r="F82">
-        <v>4003.120000000001</v>
+        <v>4053.159000000001</v>
       </c>
       <c r="G82">
         <v>207.8</v>
@@ -8139,28 +8139,28 @@
         <v>737.8</v>
       </c>
       <c r="M82">
-        <v>287.8243280000001</v>
+        <v>291.4221321000001</v>
       </c>
       <c r="N82">
-        <v>449.9756719999999</v>
+        <v>446.3778678999999</v>
       </c>
       <c r="O82">
-        <v>40.49781047999998</v>
+        <v>40.17400811099999</v>
       </c>
       <c r="P82">
-        <v>409.4778615199999</v>
+        <v>406.2038597889999</v>
       </c>
       <c r="Q82">
-        <v>536.27786152</v>
+        <v>533.003859789</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3277239371540248</v>
+        <v>0.3422742310974324</v>
       </c>
       <c r="T82">
-        <v>4.102336799460839</v>
+        <v>4.314061305331379</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.563369139525967</v>
+        <v>2.531722606939227</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1180295939085121</v>
+        <v>0.1181712003862193</v>
       </c>
       <c r="C83">
-        <v>230.4057090510578</v>
+        <v>172.3917869642073</v>
       </c>
       <c r="D83">
-        <v>4075.764709051059</v>
+        <v>4067.789786964207</v>
       </c>
       <c r="E83">
-        <v>3814.359</v>
+        <v>3864.398</v>
       </c>
       <c r="F83">
-        <v>4053.159000000001</v>
+        <v>4103.198</v>
       </c>
       <c r="G83">
         <v>207.8</v>
@@ -8221,28 +8221,28 @@
         <v>737.8</v>
       </c>
       <c r="M83">
-        <v>291.4221321000001</v>
+        <v>295.0199362</v>
       </c>
       <c r="N83">
-        <v>446.3778678999999</v>
+        <v>442.7800637999999</v>
       </c>
       <c r="O83">
-        <v>40.17400811099999</v>
+        <v>39.85020574199999</v>
       </c>
       <c r="P83">
-        <v>406.2038597889999</v>
+        <v>402.9298580579999</v>
       </c>
       <c r="Q83">
-        <v>533.003859789</v>
+        <v>529.729858058</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3422742310974324</v>
+        <v>0.3584412243678853</v>
       </c>
       <c r="T83">
-        <v>4.314061305331379</v>
+        <v>4.549310756298646</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.531722606939227</v>
+        <v>2.500847941000944</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1181712003862193</v>
+        <v>0.1212584768639265</v>
       </c>
       <c r="C84">
-        <v>172.3917869642073</v>
+        <v>-44.0750584877851</v>
       </c>
       <c r="D84">
-        <v>4067.789786964207</v>
+        <v>3901.361941512216</v>
       </c>
       <c r="E84">
-        <v>3864.398</v>
+        <v>3914.437000000001</v>
       </c>
       <c r="F84">
-        <v>4103.198</v>
+        <v>4153.237000000001</v>
       </c>
       <c r="G84">
         <v>207.8</v>
@@ -8303,45 +8303,45 @@
         <v>737.8</v>
       </c>
       <c r="M84">
-        <v>295.0199362</v>
+        <v>314.8153646000001</v>
       </c>
       <c r="N84">
-        <v>442.7800637999999</v>
+        <v>422.9846353999998</v>
       </c>
       <c r="O84">
-        <v>39.85020574199999</v>
+        <v>38.06861718599998</v>
       </c>
       <c r="P84">
-        <v>402.9298580579999</v>
+        <v>384.9160182139998</v>
       </c>
       <c r="Q84">
-        <v>529.729858058</v>
+        <v>511.7160182139999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3584412243678853</v>
+        <v>0.3765102168466268</v>
       </c>
       <c r="T84">
-        <v>4.549310756298646</v>
+        <v>4.812236613262063</v>
       </c>
       <c r="U84">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.09</v>
       </c>
       <c r="W84">
-        <v>0.065429</v>
+        <v>0.06897800000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.500847941000944</v>
+        <v>2.34359590719925</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1212584768639265</v>
+        <v>0.1214355733416337</v>
       </c>
       <c r="C85">
-        <v>-44.0750584877851</v>
+        <v>-103.2488799425246</v>
       </c>
       <c r="D85">
-        <v>3901.361941512216</v>
+        <v>3892.227120057476</v>
       </c>
       <c r="E85">
-        <v>3914.437000000001</v>
+        <v>3964.476000000001</v>
       </c>
       <c r="F85">
-        <v>4153.237000000001</v>
+        <v>4203.276000000001</v>
       </c>
       <c r="G85">
         <v>207.8</v>
@@ -8385,28 +8385,28 @@
         <v>737.8</v>
       </c>
       <c r="M85">
-        <v>314.8153646000001</v>
+        <v>318.6083208000001</v>
       </c>
       <c r="N85">
-        <v>422.9846353999998</v>
+        <v>419.1916791999999</v>
       </c>
       <c r="O85">
-        <v>38.06861718599998</v>
+        <v>37.72725112799999</v>
       </c>
       <c r="P85">
-        <v>384.9160182139998</v>
+        <v>381.4644280719999</v>
       </c>
       <c r="Q85">
-        <v>511.7160182139999</v>
+        <v>508.264428072</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3765102168466268</v>
+        <v>0.3968378333852109</v>
       </c>
       <c r="T85">
-        <v>4.812236613262063</v>
+        <v>5.108028202345906</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.34359590719925</v>
+        <v>2.315695955923069</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1214355733416337</v>
+        <v>0.1216126698193409</v>
       </c>
       <c r="C86">
-        <v>-103.2488799425246</v>
+        <v>-162.3800239738734</v>
       </c>
       <c r="D86">
-        <v>3892.227120057476</v>
+        <v>3883.134976026127</v>
       </c>
       <c r="E86">
-        <v>3964.476000000001</v>
+        <v>4014.515</v>
       </c>
       <c r="F86">
-        <v>4203.276000000001</v>
+        <v>4253.315000000001</v>
       </c>
       <c r="G86">
         <v>207.8</v>
@@ -8467,28 +8467,28 @@
         <v>737.8</v>
       </c>
       <c r="M86">
-        <v>318.6083208000001</v>
+        <v>322.4012770000001</v>
       </c>
       <c r="N86">
-        <v>419.1916791999999</v>
+        <v>415.3987229999999</v>
       </c>
       <c r="O86">
-        <v>37.72725112799999</v>
+        <v>37.38588506999999</v>
       </c>
       <c r="P86">
-        <v>381.4644280719999</v>
+        <v>378.0128379299999</v>
       </c>
       <c r="Q86">
-        <v>508.264428072</v>
+        <v>504.81283793</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3968378333852107</v>
+        <v>0.4198757987956061</v>
       </c>
       <c r="T86">
-        <v>5.108028202345903</v>
+        <v>5.443258669974258</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.315695955923069</v>
+        <v>2.28845247408868</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1216126698193409</v>
+        <v>0.1217897662970481</v>
       </c>
       <c r="C87">
-        <v>-162.3800239738734</v>
+        <v>-221.4687889649595</v>
       </c>
       <c r="D87">
-        <v>3883.134976026127</v>
+        <v>3874.085211035041</v>
       </c>
       <c r="E87">
-        <v>4014.515</v>
+        <v>4064.554</v>
       </c>
       <c r="F87">
-        <v>4253.315000000001</v>
+        <v>4303.354</v>
       </c>
       <c r="G87">
         <v>207.8</v>
@@ -8549,28 +8549,28 @@
         <v>737.8</v>
       </c>
       <c r="M87">
-        <v>322.4012770000001</v>
+        <v>326.1942332</v>
       </c>
       <c r="N87">
-        <v>415.3987229999999</v>
+        <v>411.6057667999999</v>
       </c>
       <c r="O87">
-        <v>37.38588506999999</v>
+        <v>37.04451901199999</v>
       </c>
       <c r="P87">
-        <v>378.0128379299999</v>
+        <v>374.5612477879999</v>
       </c>
       <c r="Q87">
-        <v>504.81283793</v>
+        <v>501.361247788</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4198757987956061</v>
+        <v>0.4462049021217722</v>
       </c>
       <c r="T87">
-        <v>5.443258669974258</v>
+        <v>5.826379204406664</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.28845247408868</v>
+        <v>2.261842561599277</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1217897662970481</v>
+        <v>0.1219668627747553</v>
       </c>
       <c r="C88">
-        <v>-221.4687889649595</v>
+        <v>-280.5154705238115</v>
       </c>
       <c r="D88">
-        <v>3874.085211035041</v>
+        <v>3865.077529476188</v>
       </c>
       <c r="E88">
-        <v>4064.554</v>
+        <v>4114.593</v>
       </c>
       <c r="F88">
-        <v>4303.354</v>
+        <v>4353.393</v>
       </c>
       <c r="G88">
         <v>207.8</v>
@@ -8631,28 +8631,28 @@
         <v>737.8</v>
       </c>
       <c r="M88">
-        <v>326.1942332</v>
+        <v>329.9871894</v>
       </c>
       <c r="N88">
-        <v>411.6057667999999</v>
+        <v>407.8128105999999</v>
       </c>
       <c r="O88">
-        <v>37.04451901199999</v>
+        <v>36.70315295399999</v>
       </c>
       <c r="P88">
-        <v>374.5612477879999</v>
+        <v>371.109657646</v>
       </c>
       <c r="Q88">
-        <v>501.361247788</v>
+        <v>497.909657646</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4462049021217722</v>
+        <v>0.4765846367288869</v>
       </c>
       <c r="T88">
-        <v>5.826379204406664</v>
+        <v>6.268441359520978</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.261842561599277</v>
+        <v>2.235844371236067</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1219668627747553</v>
+        <v>0.1221439592524625</v>
       </c>
       <c r="C89">
-        <v>-280.5154705238115</v>
+        <v>-339.5203615155524</v>
       </c>
       <c r="D89">
-        <v>3865.077529476188</v>
+        <v>3856.111638484448</v>
       </c>
       <c r="E89">
-        <v>4114.593</v>
+        <v>4164.632000000001</v>
       </c>
       <c r="F89">
-        <v>4353.393</v>
+        <v>4403.432000000001</v>
       </c>
       <c r="G89">
         <v>207.8</v>
@@ -8713,28 +8713,28 @@
         <v>737.8</v>
       </c>
       <c r="M89">
-        <v>329.9871894</v>
+        <v>333.7801456000001</v>
       </c>
       <c r="N89">
-        <v>407.8128105999999</v>
+        <v>404.0198543999999</v>
       </c>
       <c r="O89">
-        <v>36.70315295399999</v>
+        <v>36.36178689599998</v>
       </c>
       <c r="P89">
-        <v>371.109657646</v>
+        <v>367.6580675039999</v>
       </c>
       <c r="Q89">
-        <v>497.909657646</v>
+        <v>494.4580675039999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4765846367288869</v>
+        <v>0.5120276604371875</v>
       </c>
       <c r="T89">
-        <v>6.268441359520978</v>
+        <v>6.78418054048768</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.235844371236067</v>
+        <v>2.210437048835657</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1221439592524625</v>
+        <v>0.1223210557301697</v>
       </c>
       <c r="C90">
-        <v>-339.5203615155524</v>
+        <v>-398.4837520941314</v>
       </c>
       <c r="D90">
-        <v>3856.111638484448</v>
+        <v>3847.187247905869</v>
       </c>
       <c r="E90">
-        <v>4164.632000000001</v>
+        <v>4214.671</v>
       </c>
       <c r="F90">
-        <v>4403.432000000001</v>
+        <v>4453.471</v>
       </c>
       <c r="G90">
         <v>207.8</v>
@@ -8795,28 +8795,28 @@
         <v>737.8</v>
       </c>
       <c r="M90">
-        <v>333.7801456000001</v>
+        <v>337.5731018000001</v>
       </c>
       <c r="N90">
-        <v>404.0198543999999</v>
+        <v>400.2268981999999</v>
       </c>
       <c r="O90">
-        <v>36.36178689599998</v>
+        <v>36.02042083799999</v>
       </c>
       <c r="P90">
-        <v>367.6580675039999</v>
+        <v>364.2064773619999</v>
       </c>
       <c r="Q90">
-        <v>494.4580675039999</v>
+        <v>491.0064773619999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5120276604371875</v>
+        <v>0.5539148702742699</v>
       </c>
       <c r="T90">
-        <v>6.78418054048768</v>
+        <v>7.393690481630143</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.210437048835657</v>
+        <v>2.185600677500425</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1223210557301697</v>
+        <v>0.1224981522078769</v>
       </c>
       <c r="C91">
-        <v>-398.4837520941314</v>
+        <v>-457.4059297336339</v>
       </c>
       <c r="D91">
-        <v>3847.187247905869</v>
+        <v>3838.304070266366</v>
       </c>
       <c r="E91">
-        <v>4214.671</v>
+        <v>4264.71</v>
       </c>
       <c r="F91">
-        <v>4453.471</v>
+        <v>4503.51</v>
       </c>
       <c r="G91">
         <v>207.8</v>
@@ -8877,28 +8877,28 @@
         <v>737.8</v>
       </c>
       <c r="M91">
-        <v>337.5731018000001</v>
+        <v>341.3660580000001</v>
       </c>
       <c r="N91">
-        <v>400.2268981999999</v>
+        <v>396.4339419999999</v>
       </c>
       <c r="O91">
-        <v>36.02042083799999</v>
+        <v>35.67905477999999</v>
       </c>
       <c r="P91">
-        <v>364.2064773619999</v>
+        <v>360.7548872199999</v>
       </c>
       <c r="Q91">
-        <v>491.0064773619999</v>
+        <v>487.55488722</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5539148702742699</v>
+        <v>0.6041795220787689</v>
       </c>
       <c r="T91">
-        <v>7.393690481630143</v>
+        <v>8.125102411001102</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.185600677500425</v>
+        <v>2.161316225528198</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1224981522078769</v>
+        <v>0.1226752486855841</v>
       </c>
       <c r="C92">
-        <v>-457.4059297336339</v>
+        <v>-516.2871792591413</v>
       </c>
       <c r="D92">
-        <v>3838.304070266366</v>
+        <v>3829.461820740859</v>
       </c>
       <c r="E92">
-        <v>4264.71</v>
+        <v>4314.749000000001</v>
       </c>
       <c r="F92">
-        <v>4503.51</v>
+        <v>4553.549000000001</v>
       </c>
       <c r="G92">
         <v>207.8</v>
@@ -8959,28 +8959,28 @@
         <v>737.8</v>
       </c>
       <c r="M92">
-        <v>341.3660580000001</v>
+        <v>345.1590142000001</v>
       </c>
       <c r="N92">
-        <v>396.4339419999999</v>
+        <v>392.6409857999998</v>
       </c>
       <c r="O92">
-        <v>35.67905477999999</v>
+        <v>35.33768872199998</v>
       </c>
       <c r="P92">
-        <v>360.7548872199999</v>
+        <v>357.3032970779998</v>
       </c>
       <c r="Q92">
-        <v>487.55488722</v>
+        <v>484.1032970779999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6041795220787689</v>
+        <v>0.6656140965064898</v>
       </c>
       <c r="T92">
-        <v>8.125102411001102</v>
+        <v>9.019050324676716</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.161316225528198</v>
+        <v>2.137565497775141</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1226752486855841</v>
+        <v>0.1228523451632913</v>
       </c>
       <c r="C93">
-        <v>-516.2871792591413</v>
+        <v>-575.1277828771781</v>
       </c>
       <c r="D93">
-        <v>3829.461820740859</v>
+        <v>3820.660217122822</v>
       </c>
       <c r="E93">
-        <v>4314.749000000001</v>
+        <v>4364.788</v>
       </c>
       <c r="F93">
-        <v>4553.549000000001</v>
+        <v>4603.588000000001</v>
       </c>
       <c r="G93">
         <v>207.8</v>
@@ -9041,28 +9041,28 @@
         <v>737.8</v>
       </c>
       <c r="M93">
-        <v>345.1590142000001</v>
+        <v>348.9519704000001</v>
       </c>
       <c r="N93">
-        <v>392.6409857999998</v>
+        <v>388.8480295999999</v>
       </c>
       <c r="O93">
-        <v>35.33768872199998</v>
+        <v>34.99632266399999</v>
       </c>
       <c r="P93">
-        <v>357.3032970779998</v>
+        <v>353.8517069359999</v>
       </c>
       <c r="Q93">
-        <v>484.1032970779999</v>
+        <v>480.651706936</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6656140965064898</v>
+        <v>0.7424073145411412</v>
       </c>
       <c r="T93">
-        <v>9.019050324676716</v>
+        <v>10.13648521677124</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.137565497775141</v>
+        <v>2.114331090190628</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1228523451632913</v>
+        <v>0.1230294416409985</v>
       </c>
       <c r="C94">
-        <v>-575.1277828771781</v>
+        <v>-633.9280202057312</v>
       </c>
       <c r="D94">
-        <v>3820.660217122822</v>
+        <v>3811.898979794269</v>
       </c>
       <c r="E94">
-        <v>4364.788</v>
+        <v>4414.827</v>
       </c>
       <c r="F94">
-        <v>4603.588000000001</v>
+        <v>4653.627</v>
       </c>
       <c r="G94">
         <v>207.8</v>
@@ -9123,28 +9123,28 @@
         <v>737.8</v>
       </c>
       <c r="M94">
-        <v>348.9519704000001</v>
+        <v>352.7449266</v>
       </c>
       <c r="N94">
-        <v>388.8480295999999</v>
+        <v>385.0550733999999</v>
       </c>
       <c r="O94">
-        <v>34.99632266399999</v>
+        <v>34.65495660599999</v>
       </c>
       <c r="P94">
-        <v>353.8517069359999</v>
+        <v>350.4001167939999</v>
       </c>
       <c r="Q94">
-        <v>480.651706936</v>
+        <v>477.200116794</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7424073145411412</v>
+        <v>0.8411414520142643</v>
       </c>
       <c r="T94">
-        <v>10.13648521677124</v>
+        <v>11.57318722089276</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.114331090190628</v>
+        <v>2.091596347285352</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1230294416409985</v>
+        <v>0.1232065381187057</v>
       </c>
       <c r="C95">
-        <v>-633.9280202057312</v>
+        <v>-692.6881683038673</v>
       </c>
       <c r="D95">
-        <v>3811.898979794269</v>
+        <v>3803.177831696134</v>
       </c>
       <c r="E95">
-        <v>4414.827</v>
+        <v>4464.866000000001</v>
       </c>
       <c r="F95">
-        <v>4653.627</v>
+        <v>4703.666000000001</v>
       </c>
       <c r="G95">
         <v>207.8</v>
@@ -9205,28 +9205,28 @@
         <v>737.8</v>
       </c>
       <c r="M95">
-        <v>352.7449266</v>
+        <v>356.5378828000001</v>
       </c>
       <c r="N95">
-        <v>385.0550733999999</v>
+        <v>381.2621171999999</v>
       </c>
       <c r="O95">
-        <v>34.65495660599999</v>
+        <v>34.31359054799999</v>
       </c>
       <c r="P95">
-        <v>350.4001167939999</v>
+        <v>346.9485266519999</v>
       </c>
       <c r="Q95">
-        <v>477.200116794</v>
+        <v>473.748526652</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8411414520142643</v>
+        <v>0.9727869686450952</v>
       </c>
       <c r="T95">
-        <v>11.57318722089276</v>
+        <v>13.4887898930548</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.091596347285352</v>
+        <v>2.069345322314232</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1232065381187057</v>
+        <v>0.1233836345964129</v>
       </c>
       <c r="C96">
-        <v>-692.6881683038673</v>
+        <v>-751.4085017009324</v>
       </c>
       <c r="D96">
-        <v>3803.177831696134</v>
+        <v>3794.496498299068</v>
       </c>
       <c r="E96">
-        <v>4464.866000000001</v>
+        <v>4514.905000000001</v>
       </c>
       <c r="F96">
-        <v>4703.666000000001</v>
+        <v>4753.705000000001</v>
       </c>
       <c r="G96">
         <v>207.8</v>
@@ -9287,28 +9287,28 @@
         <v>737.8</v>
       </c>
       <c r="M96">
-        <v>356.5378828000001</v>
+        <v>360.3308390000001</v>
       </c>
       <c r="N96">
-        <v>381.2621171999999</v>
+        <v>377.4691609999999</v>
       </c>
       <c r="O96">
-        <v>34.31359054799999</v>
+        <v>33.97222448999999</v>
       </c>
       <c r="P96">
-        <v>346.9485266519999</v>
+        <v>343.4969365099999</v>
       </c>
       <c r="Q96">
-        <v>473.748526652</v>
+        <v>470.29693651</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9727869686450952</v>
+        <v>1.157090691928259</v>
       </c>
       <c r="T96">
-        <v>13.4887898930548</v>
+        <v>16.17063363408165</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.069345322314232</v>
+        <v>2.047562739974082</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1233836345964129</v>
+        <v>0.1235607310741201</v>
       </c>
       <c r="C97">
-        <v>-751.4085017009324</v>
+        <v>-810.0892924253594</v>
       </c>
       <c r="D97">
-        <v>3794.496498299068</v>
+        <v>3785.854707574641</v>
       </c>
       <c r="E97">
-        <v>4514.905000000001</v>
+        <v>4564.944</v>
       </c>
       <c r="F97">
-        <v>4753.705000000001</v>
+        <v>4803.744000000001</v>
       </c>
       <c r="G97">
         <v>207.8</v>
@@ -9369,28 +9369,28 @@
         <v>737.8</v>
       </c>
       <c r="M97">
-        <v>360.3308390000001</v>
+        <v>364.1237952000001</v>
       </c>
       <c r="N97">
-        <v>377.4691609999999</v>
+        <v>373.6762047999999</v>
       </c>
       <c r="O97">
-        <v>33.97222448999999</v>
+        <v>33.63085843199999</v>
       </c>
       <c r="P97">
-        <v>343.4969365099999</v>
+        <v>340.0453463679999</v>
       </c>
       <c r="Q97">
-        <v>470.29693651</v>
+        <v>466.845346368</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.157090691928259</v>
+        <v>1.433546276853004</v>
       </c>
       <c r="T97">
-        <v>16.17063363408165</v>
+        <v>20.19339924562192</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.047562739974082</v>
+        <v>2.026233961432685</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1235607310741201</v>
+        <v>0.1237378275518272</v>
       </c>
       <c r="C98">
-        <v>-810.0892924253594</v>
+        <v>-868.7308100330865</v>
       </c>
       <c r="D98">
-        <v>3785.854707574641</v>
+        <v>3777.252189966914</v>
       </c>
       <c r="E98">
-        <v>4564.944</v>
+        <v>4614.983</v>
       </c>
       <c r="F98">
-        <v>4803.744000000001</v>
+        <v>4853.783</v>
       </c>
       <c r="G98">
         <v>207.8</v>
@@ -9451,28 +9451,28 @@
         <v>737.8</v>
       </c>
       <c r="M98">
-        <v>364.1237952000001</v>
+        <v>367.9167514000001</v>
       </c>
       <c r="N98">
-        <v>373.6762047999999</v>
+        <v>369.8832485999999</v>
       </c>
       <c r="O98">
-        <v>33.63085843199999</v>
+        <v>33.28949237399999</v>
       </c>
       <c r="P98">
-        <v>340.0453463679999</v>
+        <v>336.5937562259999</v>
       </c>
       <c r="Q98">
-        <v>466.845346368</v>
+        <v>463.3937562259999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.433546276853</v>
+        <v>1.894305585060907</v>
       </c>
       <c r="T98">
-        <v>20.19339924562187</v>
+        <v>26.89800859818897</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.026233961432685</v>
+        <v>2.005344951521008</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1237378275518272</v>
+        <v>0.1365784840295344</v>
       </c>
       <c r="C99">
-        <v>-868.7308100330865</v>
+        <v>-1453.063793013153</v>
       </c>
       <c r="D99">
-        <v>3777.252189966914</v>
+        <v>3242.958206986847</v>
       </c>
       <c r="E99">
-        <v>4614.983</v>
+        <v>4665.022</v>
       </c>
       <c r="F99">
-        <v>4853.783</v>
+        <v>4903.822</v>
       </c>
       <c r="G99">
         <v>207.8</v>
@@ -9533,45 +9533,45 @@
         <v>737.8</v>
       </c>
       <c r="M99">
-        <v>367.9167514000001</v>
+        <v>441.34398</v>
       </c>
       <c r="N99">
-        <v>369.8832485999999</v>
+        <v>296.45602</v>
       </c>
       <c r="O99">
-        <v>33.28949237399999</v>
+        <v>26.6810418</v>
       </c>
       <c r="P99">
-        <v>336.5937562259999</v>
+        <v>269.7749782</v>
       </c>
       <c r="Q99">
-        <v>463.3937562259999</v>
+        <v>396.5749782</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.894305585060907</v>
+        <v>2.815824201476719</v>
       </c>
       <c r="T99">
-        <v>26.89800859818897</v>
+        <v>40.30722730332316</v>
       </c>
       <c r="U99">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V99">
         <v>0.09</v>
       </c>
       <c r="W99">
-        <v>0.06897800000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y99">
-        <v>2.005344951521008</v>
+        <v>1.671711937704464</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1365784840295344</v>
+        <v>0.1368848005072416</v>
       </c>
       <c r="C100">
-        <v>-1453.063793013153</v>
+        <v>-1514.008800709101</v>
       </c>
       <c r="D100">
-        <v>3242.958206986847</v>
+        <v>3232.052199290899</v>
       </c>
       <c r="E100">
-        <v>4665.022</v>
+        <v>4715.061000000001</v>
       </c>
       <c r="F100">
-        <v>4903.822</v>
+        <v>4953.861000000001</v>
       </c>
       <c r="G100">
         <v>207.8</v>
@@ -9615,28 +9615,28 @@
         <v>737.8</v>
       </c>
       <c r="M100">
-        <v>441.34398</v>
+        <v>445.8474900000001</v>
       </c>
       <c r="N100">
-        <v>296.45602</v>
+        <v>291.9525099999999</v>
       </c>
       <c r="O100">
-        <v>26.6810418</v>
+        <v>26.27572589999999</v>
       </c>
       <c r="P100">
-        <v>269.7749782</v>
+        <v>265.6767840999999</v>
       </c>
       <c r="Q100">
-        <v>396.5749782</v>
+        <v>392.4767841</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.815824201476719</v>
+        <v>5.580380050724159</v>
       </c>
       <c r="T100">
-        <v>40.30722730332316</v>
+        <v>80.53488341872576</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.671711937704464</v>
+        <v>1.654825958535731</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1368848005072416</v>
-      </c>
-      <c r="C101">
-        <v>-1514.008800709101</v>
-      </c>
-      <c r="D101">
-        <v>3232.052199290899</v>
-      </c>
-      <c r="E101">
-        <v>4715.061000000001</v>
-      </c>
-      <c r="F101">
-        <v>4953.861000000001</v>
-      </c>
-      <c r="G101">
-        <v>207.8</v>
-      </c>
-      <c r="H101">
-        <v>4765.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>864.6</v>
-      </c>
-      <c r="K101">
-        <v>126.8000000000001</v>
-      </c>
-      <c r="L101">
-        <v>737.8</v>
-      </c>
-      <c r="M101">
-        <v>445.8474900000001</v>
-      </c>
-      <c r="N101">
-        <v>291.9525099999999</v>
-      </c>
-      <c r="O101">
-        <v>26.27572589999999</v>
-      </c>
-      <c r="P101">
-        <v>265.6767840999999</v>
-      </c>
-      <c r="Q101">
-        <v>392.4767841</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.580380050724159</v>
-      </c>
-      <c r="T101">
-        <v>80.53488341872576</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.09</v>
-      </c>
-      <c r="W101">
-        <v>0.0819</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.654825958535731</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
